--- a/InputData/trans/SYBCbVT/Start Year Battery Cap by Veh Type.xlsx
+++ b/InputData/trans/SYBCbVT/Start Year Battery Cap by Veh Type.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Olivia Ashmoore\Documents\EPS_Models by Region\RMI\RMI_all_states\LA\trans\SYBCbVT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\SYBCbVT\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6DCB336C-28C3-40E2-9522-6E173D25DE14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FA0F55E-A73F-4892-A957-D4FA5443E081}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2250" yWindow="2250" windowWidth="21600" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="598" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="258">
   <si>
     <t>Sources:</t>
   </si>
@@ -916,9 +916,6 @@
   <si>
     <t>Estimated freight vehicle miles traveled by vehicle class</t>
   </si>
-  <si>
-    <t>Louisiana</t>
-  </si>
 </sst>
 </file>
 
@@ -931,7 +928,7 @@
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="0.000"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1418,7 +1415,7 @@
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="120">
+  <cellXfs count="119">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1631,7 +1628,6 @@
     <xf numFmtId="0" fontId="3" fillId="16" borderId="0" xfId="4" applyFill="1"/>
     <xf numFmtId="0" fontId="21" fillId="16" borderId="0" xfId="6" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="13" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2233,25 +2229,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="104.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="B1" t="s">
-        <v>258</v>
-      </c>
-      <c r="C1" s="104">
-        <v>45391</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -2259,97 +2249,97 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2">
       <c r="B4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="B5" s="3">
         <v>2017</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="B6" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="B7" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="B8" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2">
       <c r="B10" s="2" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="B11" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="B12" s="3">
         <v>2016</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="B13" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2">
       <c r="B14" s="4" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="B15" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:2">
       <c r="B17" s="2" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:2">
       <c r="B18" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:2">
       <c r="B19" s="3">
         <v>2022</v>
       </c>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:2">
       <c r="B20" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:2">
       <c r="B22" s="2" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:2">
       <c r="B23" t="s">
         <v>256</v>
       </c>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:2">
       <c r="B24" s="3">
         <v>2024</v>
       </c>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:2">
       <c r="B25" t="s">
         <v>257</v>
       </c>
@@ -2367,19 +2357,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="11.5703125" customWidth="1"/>
     <col min="2" max="2" width="28.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="5"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2">
       <c r="A2">
         <v>0.7</v>
       </c>
@@ -2387,7 +2377,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2">
       <c r="A3">
         <f>A2/10^3</f>
         <v>6.9999999999999999E-4</v>
@@ -2396,13 +2386,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B5" s="5"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2">
       <c r="A6">
         <v>75</v>
       </c>
@@ -2410,7 +2400,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2">
       <c r="A7">
         <v>300</v>
       </c>
@@ -2418,7 +2408,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2">
       <c r="A8">
         <f>AVERAGE(A6:A7)</f>
         <v>187.5</v>
@@ -2427,7 +2417,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2">
       <c r="A9">
         <f>A8/10^3</f>
         <v>0.1875</v>
@@ -2436,13 +2426,13 @@
         <v>16</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B11" s="5"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2">
       <c r="A12">
         <v>212</v>
       </c>
@@ -2450,7 +2440,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2">
       <c r="A13">
         <f>A12/10^3</f>
         <v>0.21199999999999999</v>
@@ -2459,13 +2449,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2">
       <c r="A15" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="5"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2">
       <c r="A16">
         <v>70</v>
       </c>
@@ -2473,7 +2463,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2">
       <c r="A17">
         <v>90</v>
       </c>
@@ -2481,7 +2471,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2">
       <c r="A18">
         <v>60</v>
       </c>
@@ -2489,7 +2479,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2">
       <c r="A19" s="7">
         <f>AVERAGE(A16:A18)</f>
         <v>73.333333333333329</v>
@@ -2498,7 +2488,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2">
       <c r="A20" s="6">
         <f>A19/10^3</f>
         <v>7.3333333333333334E-2</v>
@@ -2507,13 +2497,13 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2">
       <c r="A22" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B22" s="5"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:2">
       <c r="A23">
         <v>18.399999999999999</v>
       </c>
@@ -2521,7 +2511,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:2">
       <c r="A24">
         <v>8.8000000000000007</v>
       </c>
@@ -2529,7 +2519,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:2">
       <c r="A25">
         <f>AVERAGE(A23:A24)</f>
         <v>13.6</v>
@@ -2538,7 +2528,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:2">
       <c r="A26">
         <f>A25/10^3</f>
         <v>1.3599999999999999E-2</v>
@@ -2555,9 +2545,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97FB0092-744A-46A2-B730-2E30FDBD917B}">
   <dimension ref="A1:AG183"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33">
       <c r="A1" s="10" t="s">
         <v>41</v>
       </c>
@@ -2596,7 +2586,7 @@
       <c r="AF1" s="12"/>
       <c r="AG1" s="12"/>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33">
       <c r="A2" s="12" t="s">
         <v>43</v>
       </c>
@@ -2637,7 +2627,7 @@
       <c r="AF2" s="12"/>
       <c r="AG2" s="12"/>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33">
       <c r="A3" s="12" t="s">
         <v>45</v>
       </c>
@@ -2676,7 +2666,7 @@
       <c r="AF3" s="12"/>
       <c r="AG3" s="12"/>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33">
       <c r="A4" s="12" t="s">
         <v>46</v>
       </c>
@@ -2715,7 +2705,7 @@
       <c r="AF4" s="12"/>
       <c r="AG4" s="12"/>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33">
       <c r="A5" s="12" t="s">
         <v>47</v>
       </c>
@@ -2754,7 +2744,7 @@
       <c r="AF5" s="12"/>
       <c r="AG5" s="12"/>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33">
       <c r="A6" s="12"/>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
@@ -2789,7 +2779,7 @@
       <c r="AF6" s="12"/>
       <c r="AG6" s="12"/>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33">
       <c r="A7" s="14" t="s">
         <v>48</v>
       </c>
@@ -2820,7 +2810,7 @@
       <c r="AF7" s="12"/>
       <c r="AG7" s="12"/>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33">
       <c r="A8" s="12" t="s">
         <v>49</v>
       </c>
@@ -2866,7 +2856,7 @@
       <c r="AF8" s="12"/>
       <c r="AG8" s="12"/>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33">
       <c r="A9" s="12" t="s">
         <v>50</v>
       </c>
@@ -2912,7 +2902,7 @@
       <c r="AF9" s="12"/>
       <c r="AG9" s="12"/>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33">
       <c r="A10" s="12" t="s">
         <v>51</v>
       </c>
@@ -2958,7 +2948,7 @@
       <c r="AF10" s="12"/>
       <c r="AG10" s="12"/>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33">
       <c r="A11" s="12" t="s">
         <v>52</v>
       </c>
@@ -3004,7 +2994,7 @@
       <c r="AF11" s="12"/>
       <c r="AG11" s="12"/>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33">
       <c r="A12" s="12" t="s">
         <v>53</v>
       </c>
@@ -3051,7 +3041,7 @@
       <c r="AF12" s="12"/>
       <c r="AG12" s="12"/>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33">
       <c r="A13" s="12" t="s">
         <v>54</v>
       </c>
@@ -3097,7 +3087,7 @@
       <c r="AF13" s="12"/>
       <c r="AG13" s="12"/>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33">
       <c r="A14" s="12" t="s">
         <v>55</v>
       </c>
@@ -3143,7 +3133,7 @@
       <c r="AF14" s="12"/>
       <c r="AG14" s="12"/>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33">
       <c r="A15" s="12" t="s">
         <v>56</v>
       </c>
@@ -3189,7 +3179,7 @@
       <c r="AF15" s="12"/>
       <c r="AG15" s="12"/>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33">
       <c r="A16" s="12" t="s">
         <v>57</v>
       </c>
@@ -3235,7 +3225,7 @@
       <c r="AF16" s="12"/>
       <c r="AG16" s="12"/>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33">
       <c r="A17" s="12" t="s">
         <v>58</v>
       </c>
@@ -3281,7 +3271,7 @@
       <c r="AF17" s="12"/>
       <c r="AG17" s="12"/>
     </row>
-    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33">
       <c r="A18" s="12" t="s">
         <v>59</v>
       </c>
@@ -3328,7 +3318,7 @@
       <c r="AF18" s="12"/>
       <c r="AG18" s="12"/>
     </row>
-    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33">
       <c r="A19" s="12" t="s">
         <v>60</v>
       </c>
@@ -3374,7 +3364,7 @@
       <c r="AF19" s="12"/>
       <c r="AG19" s="12"/>
     </row>
-    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33">
       <c r="A20" s="12" t="s">
         <v>61</v>
       </c>
@@ -3420,7 +3410,7 @@
       <c r="AF20" s="12"/>
       <c r="AG20" s="12"/>
     </row>
-    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:33">
       <c r="A21" s="12" t="s">
         <v>62</v>
       </c>
@@ -3466,7 +3456,7 @@
       <c r="AF21" s="12"/>
       <c r="AG21" s="12"/>
     </row>
-    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:33">
       <c r="A22" s="12" t="s">
         <v>63</v>
       </c>
@@ -3512,7 +3502,7 @@
       <c r="AF22" s="12"/>
       <c r="AG22" s="12"/>
     </row>
-    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:33">
       <c r="A23" s="12" t="s">
         <v>64</v>
       </c>
@@ -3558,7 +3548,7 @@
       <c r="AF23" s="12"/>
       <c r="AG23" s="12"/>
     </row>
-    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:33">
       <c r="A24" s="12" t="s">
         <v>65</v>
       </c>
@@ -3605,7 +3595,7 @@
       <c r="AF24" s="12"/>
       <c r="AG24" s="12"/>
     </row>
-    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:33">
       <c r="A25" s="12" t="s">
         <v>66</v>
       </c>
@@ -3651,7 +3641,7 @@
       <c r="AF25" s="12"/>
       <c r="AG25" s="12"/>
     </row>
-    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:33">
       <c r="A26" s="12" t="s">
         <v>67</v>
       </c>
@@ -3697,7 +3687,7 @@
       <c r="AF26" s="12"/>
       <c r="AG26" s="12"/>
     </row>
-    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:33">
       <c r="A27" s="12" t="s">
         <v>68</v>
       </c>
@@ -3743,7 +3733,7 @@
       <c r="AF27" s="12"/>
       <c r="AG27" s="12"/>
     </row>
-    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:33">
       <c r="A28" s="12" t="s">
         <v>69</v>
       </c>
@@ -3789,7 +3779,7 @@
       <c r="AF28" s="12"/>
       <c r="AG28" s="12"/>
     </row>
-    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:33">
       <c r="A29" s="12" t="s">
         <v>70</v>
       </c>
@@ -3835,7 +3825,7 @@
       <c r="AF29" s="12"/>
       <c r="AG29" s="12"/>
     </row>
-    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:33">
       <c r="A30" s="12" t="s">
         <v>71</v>
       </c>
@@ -3882,7 +3872,7 @@
       <c r="AF30" s="12"/>
       <c r="AG30" s="12"/>
     </row>
-    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:33">
       <c r="A31" s="12" t="s">
         <v>72</v>
       </c>
@@ -3928,7 +3918,7 @@
       <c r="AF31" s="12"/>
       <c r="AG31" s="12"/>
     </row>
-    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:33">
       <c r="A32" s="12" t="s">
         <v>73</v>
       </c>
@@ -3974,7 +3964,7 @@
       <c r="AF32" s="12"/>
       <c r="AG32" s="12"/>
     </row>
-    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:33">
       <c r="A33" s="12"/>
       <c r="B33" s="12"/>
       <c r="C33" s="12"/>
@@ -4008,7 +3998,7 @@
       <c r="AF33" s="12"/>
       <c r="AG33" s="12"/>
     </row>
-    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:33">
       <c r="A34" s="12"/>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
@@ -4042,7 +4032,7 @@
       <c r="AF34" s="12"/>
       <c r="AG34" s="12"/>
     </row>
-    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:33">
       <c r="A35" s="14" t="s">
         <v>74</v>
       </c>
@@ -4088,7 +4078,7 @@
       <c r="AF35" s="12"/>
       <c r="AG35" s="12"/>
     </row>
-    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:33">
       <c r="A36" s="12" t="s">
         <v>75</v>
       </c>
@@ -4134,7 +4124,7 @@
       <c r="AF36" s="12"/>
       <c r="AG36" s="12"/>
     </row>
-    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:33">
       <c r="A37" s="12" t="s">
         <v>76</v>
       </c>
@@ -4180,7 +4170,7 @@
       <c r="AF37" s="12"/>
       <c r="AG37" s="12"/>
     </row>
-    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:33">
       <c r="A38" s="12" t="s">
         <v>77</v>
       </c>
@@ -4226,7 +4216,7 @@
       <c r="AF38" s="12"/>
       <c r="AG38" s="12"/>
     </row>
-    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:33">
       <c r="A39" s="12" t="s">
         <v>78</v>
       </c>
@@ -4273,7 +4263,7 @@
       <c r="AF39" s="12"/>
       <c r="AG39" s="12"/>
     </row>
-    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:33">
       <c r="A40" s="12" t="s">
         <v>79</v>
       </c>
@@ -4319,7 +4309,7 @@
       <c r="AF40" s="12"/>
       <c r="AG40" s="12"/>
     </row>
-    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:33">
       <c r="A41" s="12" t="s">
         <v>80</v>
       </c>
@@ -4365,7 +4355,7 @@
       <c r="AF41" s="12"/>
       <c r="AG41" s="12"/>
     </row>
-    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:33">
       <c r="A42" s="12" t="s">
         <v>81</v>
       </c>
@@ -4411,7 +4401,7 @@
       <c r="AF42" s="12"/>
       <c r="AG42" s="12"/>
     </row>
-    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:33">
       <c r="A43" s="12" t="s">
         <v>82</v>
       </c>
@@ -4457,7 +4447,7 @@
       <c r="AF43" s="12"/>
       <c r="AG43" s="12"/>
     </row>
-    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:33">
       <c r="A44" s="12" t="s">
         <v>83</v>
       </c>
@@ -4503,7 +4493,7 @@
       <c r="AF44" s="12"/>
       <c r="AG44" s="12"/>
     </row>
-    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:33">
       <c r="A45" s="12" t="s">
         <v>84</v>
       </c>
@@ -4550,7 +4540,7 @@
       <c r="AF45" s="12"/>
       <c r="AG45" s="12"/>
     </row>
-    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:33">
       <c r="A46" s="12" t="s">
         <v>85</v>
       </c>
@@ -4596,7 +4586,7 @@
       <c r="AF46" s="12"/>
       <c r="AG46" s="12"/>
     </row>
-    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:33">
       <c r="A47" s="12" t="s">
         <v>86</v>
       </c>
@@ -4642,7 +4632,7 @@
       <c r="AF47" s="12"/>
       <c r="AG47" s="12"/>
     </row>
-    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:33">
       <c r="A48" s="12" t="s">
         <v>87</v>
       </c>
@@ -4688,7 +4678,7 @@
       <c r="AF48" s="12"/>
       <c r="AG48" s="12"/>
     </row>
-    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:33">
       <c r="A49" s="12" t="s">
         <v>88</v>
       </c>
@@ -4734,7 +4724,7 @@
       <c r="AF49" s="12"/>
       <c r="AG49" s="12"/>
     </row>
-    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:33">
       <c r="A50" s="12" t="s">
         <v>89</v>
       </c>
@@ -4780,7 +4770,7 @@
       <c r="AF50" s="12"/>
       <c r="AG50" s="12"/>
     </row>
-    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:33">
       <c r="A51" s="12" t="s">
         <v>90</v>
       </c>
@@ -4827,7 +4817,7 @@
       <c r="AF51" s="12"/>
       <c r="AG51" s="12"/>
     </row>
-    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:33">
       <c r="A52" s="12" t="s">
         <v>91</v>
       </c>
@@ -4873,7 +4863,7 @@
       <c r="AF52" s="12"/>
       <c r="AG52" s="12"/>
     </row>
-    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:33">
       <c r="A53" s="12" t="s">
         <v>92</v>
       </c>
@@ -4919,7 +4909,7 @@
       <c r="AF53" s="12"/>
       <c r="AG53" s="12"/>
     </row>
-    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:33">
       <c r="A54" s="12" t="s">
         <v>93</v>
       </c>
@@ -4965,7 +4955,7 @@
       <c r="AF54" s="12"/>
       <c r="AG54" s="12"/>
     </row>
-    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:33">
       <c r="A55" s="12" t="s">
         <v>94</v>
       </c>
@@ -5011,7 +5001,7 @@
       <c r="AF55" s="12"/>
       <c r="AG55" s="12"/>
     </row>
-    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:33">
       <c r="A56" s="12" t="s">
         <v>95</v>
       </c>
@@ -5057,7 +5047,7 @@
       <c r="AF56" s="12"/>
       <c r="AG56" s="12"/>
     </row>
-    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:33">
       <c r="A57" s="12" t="s">
         <v>96</v>
       </c>
@@ -5104,7 +5094,7 @@
       <c r="AF57" s="12"/>
       <c r="AG57" s="12"/>
     </row>
-    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:33">
       <c r="A58" s="12" t="s">
         <v>97</v>
       </c>
@@ -5150,7 +5140,7 @@
       <c r="AF58" s="12"/>
       <c r="AG58" s="12"/>
     </row>
-    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:33">
       <c r="A59" s="12" t="s">
         <v>98</v>
       </c>
@@ -5196,7 +5186,7 @@
       <c r="AF59" s="12"/>
       <c r="AG59" s="12"/>
     </row>
-    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:33">
       <c r="A60" s="12"/>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
@@ -5230,7 +5220,7 @@
       <c r="AF60" s="12"/>
       <c r="AG60" s="12"/>
     </row>
-    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:33">
       <c r="A61" s="17" t="s">
         <v>99</v>
       </c>
@@ -5266,7 +5256,7 @@
       <c r="AF61" s="12"/>
       <c r="AG61" s="12"/>
     </row>
-    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:33">
       <c r="A62" s="18" t="s">
         <v>100</v>
       </c>
@@ -5302,7 +5292,7 @@
       <c r="AF62" s="12"/>
       <c r="AG62" s="12"/>
     </row>
-    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:33">
       <c r="A63" s="12"/>
       <c r="C63" s="20">
         <v>2020</v>
@@ -5367,7 +5357,7 @@
       <c r="AF63" s="12"/>
       <c r="AG63" s="12"/>
     </row>
-    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:33">
       <c r="A64" s="21" t="s">
         <v>50</v>
       </c>
@@ -5451,7 +5441,7 @@
       <c r="AF64" s="12"/>
       <c r="AG64" s="12"/>
     </row>
-    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:33">
       <c r="A65" s="21" t="s">
         <v>51</v>
       </c>
@@ -5535,7 +5525,7 @@
       <c r="AF65" s="12"/>
       <c r="AG65" s="12"/>
     </row>
-    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:33">
       <c r="A66" s="21" t="s">
         <v>52</v>
       </c>
@@ -5619,7 +5609,7 @@
       <c r="AF66" s="12"/>
       <c r="AG66" s="12"/>
     </row>
-    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:33">
       <c r="A67" s="21" t="s">
         <v>53</v>
       </c>
@@ -5703,7 +5693,7 @@
       <c r="AF67" s="12"/>
       <c r="AG67" s="12"/>
     </row>
-    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:33">
       <c r="A68" s="21" t="s">
         <v>54</v>
       </c>
@@ -5787,7 +5777,7 @@
       <c r="AF68" s="12"/>
       <c r="AG68" s="12"/>
     </row>
-    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:33">
       <c r="A69" s="21" t="s">
         <v>55</v>
       </c>
@@ -5871,7 +5861,7 @@
       <c r="AF69" s="12"/>
       <c r="AG69" s="12"/>
     </row>
-    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:33">
       <c r="A70" s="21" t="s">
         <v>56</v>
       </c>
@@ -5955,7 +5945,7 @@
       <c r="AF70" s="12"/>
       <c r="AG70" s="12"/>
     </row>
-    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:33">
       <c r="A71" s="21" t="s">
         <v>57</v>
       </c>
@@ -6039,7 +6029,7 @@
       <c r="AF71" s="12"/>
       <c r="AG71" s="12"/>
     </row>
-    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:33">
       <c r="A72" s="21" t="s">
         <v>58</v>
       </c>
@@ -6123,7 +6113,7 @@
       <c r="AF72" s="12"/>
       <c r="AG72" s="12"/>
     </row>
-    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:33">
       <c r="A73" s="21" t="s">
         <v>59</v>
       </c>
@@ -6207,7 +6197,7 @@
       <c r="AF73" s="12"/>
       <c r="AG73" s="12"/>
     </row>
-    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:33">
       <c r="A74" s="21" t="s">
         <v>60</v>
       </c>
@@ -6291,7 +6281,7 @@
       <c r="AF74" s="12"/>
       <c r="AG74" s="12"/>
     </row>
-    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:33">
       <c r="A75" s="21" t="s">
         <v>61</v>
       </c>
@@ -6375,7 +6365,7 @@
       <c r="AF75" s="12"/>
       <c r="AG75" s="12"/>
     </row>
-    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:33">
       <c r="A76" s="21" t="s">
         <v>62</v>
       </c>
@@ -6459,7 +6449,7 @@
       <c r="AF76" s="12"/>
       <c r="AG76" s="12"/>
     </row>
-    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:33">
       <c r="A77" s="21" t="s">
         <v>63</v>
       </c>
@@ -6543,7 +6533,7 @@
       <c r="AF77" s="12"/>
       <c r="AG77" s="12"/>
     </row>
-    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:33">
       <c r="A78" s="21" t="s">
         <v>64</v>
       </c>
@@ -6627,7 +6617,7 @@
       <c r="AF78" s="12"/>
       <c r="AG78" s="12"/>
     </row>
-    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:33">
       <c r="A79" s="21" t="s">
         <v>65</v>
       </c>
@@ -6711,7 +6701,7 @@
       <c r="AF79" s="12"/>
       <c r="AG79" s="12"/>
     </row>
-    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:33">
       <c r="A80" s="21" t="s">
         <v>66</v>
       </c>
@@ -6795,7 +6785,7 @@
       <c r="AF80" s="12"/>
       <c r="AG80" s="12"/>
     </row>
-    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:33">
       <c r="A81" s="21" t="s">
         <v>67</v>
       </c>
@@ -6879,7 +6869,7 @@
       <c r="AF81" s="12"/>
       <c r="AG81" s="12"/>
     </row>
-    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:33">
       <c r="A82" s="21" t="s">
         <v>68</v>
       </c>
@@ -6963,7 +6953,7 @@
       <c r="AF82" s="12"/>
       <c r="AG82" s="12"/>
     </row>
-    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:33">
       <c r="A83" s="21" t="s">
         <v>69</v>
       </c>
@@ -7047,7 +7037,7 @@
       <c r="AF83" s="12"/>
       <c r="AG83" s="12"/>
     </row>
-    <row r="84" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:33">
       <c r="A84" s="21" t="s">
         <v>70</v>
       </c>
@@ -7131,7 +7121,7 @@
       <c r="AF84" s="12"/>
       <c r="AG84" s="12"/>
     </row>
-    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:33">
       <c r="A85" s="21" t="s">
         <v>71</v>
       </c>
@@ -7215,7 +7205,7 @@
       <c r="AF85" s="12"/>
       <c r="AG85" s="12"/>
     </row>
-    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:33">
       <c r="A86" s="21" t="s">
         <v>72</v>
       </c>
@@ -7299,7 +7289,7 @@
       <c r="AF86" s="12"/>
       <c r="AG86" s="12"/>
     </row>
-    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:33">
       <c r="A87" s="21" t="s">
         <v>73</v>
       </c>
@@ -7383,7 +7373,7 @@
       <c r="AF87" s="12"/>
       <c r="AG87" s="12"/>
     </row>
-    <row r="89" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:33">
       <c r="A89" s="17" t="s">
         <v>101</v>
       </c>
@@ -7420,7 +7410,7 @@
       <c r="AF89" s="12"/>
       <c r="AG89" s="12"/>
     </row>
-    <row r="90" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:33">
       <c r="A90" s="18" t="s">
         <v>102</v>
       </c>
@@ -7457,7 +7447,7 @@
       <c r="AF90" s="12"/>
       <c r="AG90" s="12"/>
     </row>
-    <row r="91" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:33">
       <c r="A91" s="12"/>
       <c r="C91" s="20">
         <v>2020</v>
@@ -7523,7 +7513,7 @@
       <c r="AF91" s="12"/>
       <c r="AG91" s="12"/>
     </row>
-    <row r="92" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:33">
       <c r="A92" s="21" t="s">
         <v>75</v>
       </c>
@@ -7607,7 +7597,7 @@
       <c r="AF92" s="12"/>
       <c r="AG92" s="12"/>
     </row>
-    <row r="93" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:33">
       <c r="A93" s="21" t="s">
         <v>76</v>
       </c>
@@ -7691,7 +7681,7 @@
       <c r="AF93" s="12"/>
       <c r="AG93" s="12"/>
     </row>
-    <row r="94" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:33">
       <c r="A94" s="21" t="s">
         <v>77</v>
       </c>
@@ -7775,7 +7765,7 @@
       <c r="AF94" s="12"/>
       <c r="AG94" s="12"/>
     </row>
-    <row r="95" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:33">
       <c r="A95" s="21" t="s">
         <v>78</v>
       </c>
@@ -7859,7 +7849,7 @@
       <c r="AF95" s="12"/>
       <c r="AG95" s="12"/>
     </row>
-    <row r="96" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:33">
       <c r="A96" s="21" t="s">
         <v>79</v>
       </c>
@@ -7943,7 +7933,7 @@
       <c r="AF96" s="12"/>
       <c r="AG96" s="12"/>
     </row>
-    <row r="97" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:33">
       <c r="A97" s="21" t="s">
         <v>80</v>
       </c>
@@ -8027,7 +8017,7 @@
       <c r="AF97" s="12"/>
       <c r="AG97" s="12"/>
     </row>
-    <row r="98" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:33">
       <c r="A98" s="21" t="s">
         <v>81</v>
       </c>
@@ -8111,7 +8101,7 @@
       <c r="AF98" s="12"/>
       <c r="AG98" s="12"/>
     </row>
-    <row r="99" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:33">
       <c r="A99" s="21" t="s">
         <v>82</v>
       </c>
@@ -8195,7 +8185,7 @@
       <c r="AF99" s="12"/>
       <c r="AG99" s="12"/>
     </row>
-    <row r="100" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:33">
       <c r="A100" s="21" t="s">
         <v>83</v>
       </c>
@@ -8279,7 +8269,7 @@
       <c r="AF100" s="12"/>
       <c r="AG100" s="12"/>
     </row>
-    <row r="101" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:33">
       <c r="A101" s="21" t="s">
         <v>84</v>
       </c>
@@ -8363,7 +8353,7 @@
       <c r="AF101" s="12"/>
       <c r="AG101" s="12"/>
     </row>
-    <row r="102" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:33">
       <c r="A102" s="21" t="s">
         <v>85</v>
       </c>
@@ -8447,7 +8437,7 @@
       <c r="AF102" s="12"/>
       <c r="AG102" s="12"/>
     </row>
-    <row r="103" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:33">
       <c r="A103" s="21" t="s">
         <v>86</v>
       </c>
@@ -8531,7 +8521,7 @@
       <c r="AF103" s="12"/>
       <c r="AG103" s="12"/>
     </row>
-    <row r="104" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:33">
       <c r="A104" s="21" t="s">
         <v>87</v>
       </c>
@@ -8615,7 +8605,7 @@
       <c r="AF104" s="12"/>
       <c r="AG104" s="12"/>
     </row>
-    <row r="105" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:33">
       <c r="A105" s="21" t="s">
         <v>88</v>
       </c>
@@ -8699,7 +8689,7 @@
       <c r="AF105" s="12"/>
       <c r="AG105" s="12"/>
     </row>
-    <row r="106" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:33">
       <c r="A106" s="21" t="s">
         <v>89</v>
       </c>
@@ -8783,7 +8773,7 @@
       <c r="AF106" s="12"/>
       <c r="AG106" s="12"/>
     </row>
-    <row r="107" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:33">
       <c r="A107" s="21" t="s">
         <v>90</v>
       </c>
@@ -8867,7 +8857,7 @@
       <c r="AF107" s="12"/>
       <c r="AG107" s="12"/>
     </row>
-    <row r="108" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:33">
       <c r="A108" s="21" t="s">
         <v>91</v>
       </c>
@@ -8951,7 +8941,7 @@
       <c r="AF108" s="12"/>
       <c r="AG108" s="12"/>
     </row>
-    <row r="109" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:33">
       <c r="A109" s="21" t="s">
         <v>92</v>
       </c>
@@ -9035,7 +9025,7 @@
       <c r="AF109" s="12"/>
       <c r="AG109" s="12"/>
     </row>
-    <row r="110" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:33">
       <c r="A110" s="21" t="s">
         <v>93</v>
       </c>
@@ -9111,7 +9101,7 @@
       <c r="AF110" s="12"/>
       <c r="AG110" s="12"/>
     </row>
-    <row r="111" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:33">
       <c r="A111" s="21" t="s">
         <v>94</v>
       </c>
@@ -9187,7 +9177,7 @@
       <c r="AF111" s="12"/>
       <c r="AG111" s="12"/>
     </row>
-    <row r="112" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:33">
       <c r="A112" s="21" t="s">
         <v>95</v>
       </c>
@@ -9263,7 +9253,7 @@
       <c r="AF112" s="12"/>
       <c r="AG112" s="12"/>
     </row>
-    <row r="113" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:33">
       <c r="A113" s="21" t="s">
         <v>96</v>
       </c>
@@ -9349,7 +9339,7 @@
       <c r="AF113" s="12"/>
       <c r="AG113" s="12"/>
     </row>
-    <row r="114" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:33">
       <c r="A114" s="21" t="s">
         <v>97</v>
       </c>
@@ -9425,7 +9415,7 @@
       <c r="AF114" s="12"/>
       <c r="AG114" s="12"/>
     </row>
-    <row r="115" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:33">
       <c r="A115" s="21" t="s">
         <v>98</v>
       </c>
@@ -9501,8 +9491,8 @@
       <c r="AF115" s="12"/>
       <c r="AG115" s="12"/>
     </row>
-    <row r="117" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="118" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:33" ht="15.75" thickBot="1"/>
+    <row r="118" spans="1:33" ht="15.75" thickBot="1">
       <c r="A118" s="20" t="s">
         <v>104</v>
       </c>
@@ -9522,7 +9512,7 @@
       <c r="O118" s="12"/>
       <c r="P118" s="12"/>
       <c r="Q118" s="27"/>
-      <c r="R118" s="107"/>
+      <c r="R118" s="106"/>
       <c r="S118" s="28"/>
       <c r="T118" s="29"/>
       <c r="U118" s="29"/>
@@ -9537,25 +9527,25 @@
       <c r="AD118" s="29"/>
       <c r="AE118" s="29"/>
     </row>
-    <row r="119" spans="1:33" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="110" t="s">
+    <row r="119" spans="1:33" ht="23.25" thickBot="1">
+      <c r="A119" s="109" t="s">
         <v>49</v>
       </c>
-      <c r="B119" s="112" t="s">
+      <c r="B119" s="111" t="s">
         <v>105</v>
       </c>
-      <c r="C119" s="113" t="s">
+      <c r="C119" s="112" t="s">
         <v>106</v>
       </c>
-      <c r="D119" s="114"/>
-      <c r="E119" s="114"/>
-      <c r="F119" s="114"/>
-      <c r="G119" s="113" t="s">
+      <c r="D119" s="113"/>
+      <c r="E119" s="113"/>
+      <c r="F119" s="113"/>
+      <c r="G119" s="112" t="s">
         <v>107</v>
       </c>
-      <c r="H119" s="114"/>
-      <c r="I119" s="114"/>
-      <c r="J119" s="114"/>
+      <c r="H119" s="113"/>
+      <c r="I119" s="113"/>
+      <c r="J119" s="113"/>
       <c r="K119" s="12"/>
       <c r="L119" s="12"/>
       <c r="M119" s="12"/>
@@ -9563,8 +9553,8 @@
       <c r="O119" s="12"/>
       <c r="P119" s="12"/>
       <c r="Q119" s="27"/>
-      <c r="R119" s="108"/>
-      <c r="S119" s="115" t="s">
+      <c r="R119" s="107"/>
+      <c r="S119" s="114" t="s">
         <v>108</v>
       </c>
       <c r="T119" s="28" t="s">
@@ -9604,9 +9594,9 @@
         <v>111</v>
       </c>
     </row>
-    <row r="120" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="111"/>
-      <c r="B120" s="112"/>
+    <row r="120" spans="1:33" ht="15.75" thickBot="1">
+      <c r="A120" s="110"/>
+      <c r="B120" s="111"/>
       <c r="C120" s="31">
         <v>2020</v>
       </c>
@@ -9638,8 +9628,8 @@
       <c r="O120" s="12"/>
       <c r="P120" s="12"/>
       <c r="Q120" s="27"/>
-      <c r="R120" s="109"/>
-      <c r="S120" s="116"/>
+      <c r="R120" s="108"/>
+      <c r="S120" s="115"/>
       <c r="T120" s="33">
         <v>2022</v>
       </c>
@@ -9677,7 +9667,7 @@
         <v>2035</v>
       </c>
     </row>
-    <row r="121" spans="1:33" ht="34.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:33" ht="34.5" thickBot="1">
       <c r="A121" s="35" t="s">
         <v>109</v>
       </c>
@@ -9748,7 +9738,7 @@
         <v>252.86951483455164</v>
       </c>
     </row>
-    <row r="122" spans="1:33" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:33" ht="23.25" thickBot="1">
       <c r="A122" s="41" t="s">
         <v>110</v>
       </c>
@@ -9777,41 +9767,41 @@
       <c r="N122" s="12"/>
       <c r="O122" s="12"/>
       <c r="P122" s="12"/>
-      <c r="Q122" s="117"/>
+      <c r="Q122" s="116"/>
       <c r="R122" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="S122" s="118"/>
-      <c r="T122" s="105" t="s">
+      <c r="S122" s="117"/>
+      <c r="T122" s="104" t="s">
         <v>115</v>
       </c>
-      <c r="U122" s="105" t="s">
+      <c r="U122" s="104" t="s">
         <v>115</v>
       </c>
-      <c r="V122" s="105" t="s">
+      <c r="V122" s="104" t="s">
         <v>115</v>
       </c>
-      <c r="W122" s="105" t="s">
+      <c r="W122" s="104" t="s">
         <v>115</v>
       </c>
-      <c r="X122" s="105" t="s">
+      <c r="X122" s="104" t="s">
         <v>115</v>
       </c>
-      <c r="Y122" s="105" t="s">
+      <c r="Y122" s="104" t="s">
         <v>115</v>
       </c>
-      <c r="Z122" s="105" t="s">
+      <c r="Z122" s="104" t="s">
         <v>115</v>
       </c>
-      <c r="AA122" s="105" t="s">
+      <c r="AA122" s="104" t="s">
         <v>115</v>
       </c>
-      <c r="AB122" s="105"/>
-      <c r="AC122" s="105"/>
-      <c r="AD122" s="105"/>
-      <c r="AE122" s="105"/>
-    </row>
-    <row r="123" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="AB122" s="104"/>
+      <c r="AC122" s="104"/>
+      <c r="AD122" s="104"/>
+      <c r="AE122" s="104"/>
+    </row>
+    <row r="123" spans="1:33" ht="15.75" thickBot="1">
       <c r="A123" s="35" t="s">
         <v>46</v>
       </c>
@@ -9840,25 +9830,25 @@
       <c r="N123" s="12"/>
       <c r="O123" s="12"/>
       <c r="P123" s="12"/>
-      <c r="Q123" s="117"/>
+      <c r="Q123" s="116"/>
       <c r="R123" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="S123" s="119"/>
-      <c r="T123" s="106"/>
-      <c r="U123" s="106"/>
-      <c r="V123" s="106"/>
-      <c r="W123" s="106"/>
-      <c r="X123" s="106"/>
-      <c r="Y123" s="106"/>
-      <c r="Z123" s="106"/>
-      <c r="AA123" s="106"/>
-      <c r="AB123" s="106"/>
-      <c r="AC123" s="106"/>
-      <c r="AD123" s="106"/>
-      <c r="AE123" s="106"/>
-    </row>
-    <row r="124" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="S123" s="118"/>
+      <c r="T123" s="105"/>
+      <c r="U123" s="105"/>
+      <c r="V123" s="105"/>
+      <c r="W123" s="105"/>
+      <c r="X123" s="105"/>
+      <c r="Y123" s="105"/>
+      <c r="Z123" s="105"/>
+      <c r="AA123" s="105"/>
+      <c r="AB123" s="105"/>
+      <c r="AC123" s="105"/>
+      <c r="AD123" s="105"/>
+      <c r="AE123" s="105"/>
+    </row>
+    <row r="124" spans="1:33" ht="15.75" thickBot="1">
       <c r="A124" s="41" t="s">
         <v>111</v>
       </c>
@@ -9931,7 +9921,7 @@
         <v>0.30309995733807726</v>
       </c>
     </row>
-    <row r="125" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:33" ht="15.75" thickBot="1">
       <c r="A125" s="35" t="s">
         <v>109</v>
       </c>
@@ -10014,7 +10004,7 @@
         <v>0.31939450393345609</v>
       </c>
     </row>
-    <row r="126" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:33" ht="15.75" thickBot="1">
       <c r="A126" s="41" t="s">
         <v>109</v>
       </c>
@@ -10095,7 +10085,7 @@
         <v>0.33656503959554668</v>
       </c>
     </row>
-    <row r="127" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:33" ht="15.75" thickBot="1">
       <c r="A127" s="35" t="s">
         <v>109</v>
       </c>
@@ -10176,7 +10166,7 @@
         <v>0.35465865718701378</v>
       </c>
     </row>
-    <row r="128" spans="1:33" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:33" ht="15.75" thickBot="1">
       <c r="A128" s="41" t="s">
         <v>109</v>
       </c>
@@ -10257,7 +10247,7 @@
         <v>0.37372498126617681</v>
       </c>
     </row>
-    <row r="129" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:31" ht="15.75" thickBot="1">
       <c r="A129" s="35" t="s">
         <v>109</v>
       </c>
@@ -10338,7 +10328,7 @@
         <v>0.3927913053453399</v>
       </c>
     </row>
-    <row r="130" spans="1:31" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:31" ht="23.25" thickBot="1">
       <c r="A130" s="41" t="s">
         <v>109</v>
       </c>
@@ -10421,7 +10411,7 @@
         <v>43.366609280678752</v>
       </c>
     </row>
-    <row r="131" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:31" ht="15.75" thickBot="1">
       <c r="A131" s="35" t="s">
         <v>110</v>
       </c>
@@ -10504,7 +10494,7 @@
         <v>60.930643827305474</v>
       </c>
     </row>
-    <row r="132" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:31" ht="15.75" thickBot="1">
       <c r="A132" s="41" t="s">
         <v>110</v>
       </c>
@@ -10585,7 +10575,7 @@
         <v>80.257817134322678</v>
       </c>
     </row>
-    <row r="133" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:31" ht="15.75" thickBot="1">
       <c r="A133" s="35" t="s">
         <v>110</v>
       </c>
@@ -10666,7 +10656,7 @@
         <v>101.48693882582241</v>
       </c>
     </row>
-    <row r="134" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:31" ht="15.75" thickBot="1">
       <c r="A134" s="41" t="s">
         <v>110</v>
       </c>
@@ -10747,7 +10737,7 @@
         <v>124.76664759193905</v>
       </c>
     </row>
-    <row r="135" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:31" ht="15.75" thickBot="1">
       <c r="A135" s="35" t="s">
         <v>110</v>
       </c>
@@ -10828,7 +10818,7 @@
         <v>149.86499034714507</v>
       </c>
     </row>
-    <row r="136" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:31" ht="15.75" thickBot="1">
       <c r="A136" s="41" t="s">
         <v>110</v>
       </c>
@@ -10911,7 +10901,7 @@
         <v>64.187199212787178</v>
       </c>
     </row>
-    <row r="137" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:31" ht="15.75" thickBot="1">
       <c r="A137" s="35" t="s">
         <v>46</v>
       </c>
@@ -10994,7 +10984,7 @@
         <v>61.594360138983198</v>
       </c>
     </row>
-    <row r="138" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:31" ht="15.75" thickBot="1">
       <c r="A138" s="41" t="s">
         <v>46</v>
       </c>
@@ -11075,7 +11065,7 @@
         <v>59.493624410996297</v>
       </c>
     </row>
-    <row r="139" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:31" ht="15.75" thickBot="1">
       <c r="A139" s="35" t="s">
         <v>46</v>
       </c>
@@ -11156,7 +11146,7 @@
         <v>57.704154570920309</v>
       </c>
     </row>
-    <row r="140" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:31" ht="15.75" thickBot="1">
       <c r="A140" s="41" t="s">
         <v>46</v>
       </c>
@@ -11237,7 +11227,7 @@
         <v>56.691118280256852</v>
       </c>
     </row>
-    <row r="141" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:31" ht="15.75" thickBot="1">
       <c r="A141" s="35" t="s">
         <v>46</v>
       </c>
@@ -11318,7 +11308,7 @@
         <v>56.691118280256852</v>
       </c>
     </row>
-    <row r="142" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:31" ht="15.75" thickBot="1">
       <c r="A142" s="41" t="s">
         <v>46</v>
       </c>
@@ -11401,7 +11391,7 @@
         <v>0.44039766865078672</v>
       </c>
     </row>
-    <row r="143" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:31" ht="15.75" thickBot="1">
       <c r="A143" s="35" t="s">
         <v>111</v>
       </c>
@@ -11484,7 +11474,7 @@
         <v>0.4423415530336538</v>
       </c>
     </row>
-    <row r="144" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:31" ht="15.75" thickBot="1">
       <c r="A144" s="41" t="s">
         <v>111</v>
       </c>
@@ -11565,7 +11555,7 @@
         <v>0.44429401758567916</v>
       </c>
     </row>
-    <row r="145" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:31" ht="15.75" thickBot="1">
       <c r="A145" s="35" t="s">
         <v>111</v>
       </c>
@@ -11646,7 +11636,7 @@
         <v>0.44625510017912701</v>
       </c>
     </row>
-    <row r="146" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:31" ht="15.75" thickBot="1">
       <c r="A146" s="41" t="s">
         <v>111</v>
       </c>
@@ -11727,7 +11717,7 @@
         <v>0.44822483885342695</v>
       </c>
     </row>
-    <row r="147" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:31" ht="15.75" thickBot="1">
       <c r="A147" s="35" t="s">
         <v>111</v>
       </c>
@@ -11808,7 +11798,7 @@
         <v>0.45020327181591202</v>
       </c>
     </row>
-    <row r="148" spans="1:31" ht="23.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:31" ht="23.25" thickBot="1">
       <c r="A148" s="41" t="s">
         <v>111</v>
       </c>
@@ -11891,7 +11881,7 @@
         <v>9.3256645451888076</v>
       </c>
     </row>
-    <row r="149" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:31" ht="15.75" thickBot="1">
       <c r="A149" s="35" t="s">
         <v>109</v>
       </c>
@@ -11974,7 +11964,7 @@
         <v>14.05024106040643</v>
       </c>
     </row>
-    <row r="150" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:31" ht="15.75" thickBot="1">
       <c r="A150" s="41" t="s">
         <v>109</v>
       </c>
@@ -12055,7 +12045,7 @@
         <v>18.816343783707534</v>
       </c>
     </row>
-    <row r="151" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:31" ht="15.75" thickBot="1">
       <c r="A151" s="35" t="s">
         <v>109</v>
       </c>
@@ -12136,7 +12126,7 @@
         <v>23.62424725475854</v>
       </c>
     </row>
-    <row r="152" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:31" ht="15.75" thickBot="1">
       <c r="A152" s="41" t="s">
         <v>109</v>
       </c>
@@ -12217,7 +12207,7 @@
         <v>28.474227627777672</v>
       </c>
     </row>
-    <row r="153" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:31" ht="15.75" thickBot="1">
       <c r="A153" s="35" t="s">
         <v>109</v>
       </c>
@@ -12298,7 +12288,7 @@
         <v>33.366562680439209</v>
       </c>
     </row>
-    <row r="154" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:31" ht="15.75" thickBot="1">
       <c r="A154" s="41" t="s">
         <v>109</v>
       </c>
@@ -12381,7 +12371,7 @@
         <v>83.61781376609099</v>
       </c>
     </row>
-    <row r="155" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:31" ht="15.75" thickBot="1">
       <c r="A155" s="35" t="s">
         <v>110</v>
       </c>
@@ -12464,7 +12454,7 @@
         <v>83.61781376609099</v>
       </c>
     </row>
-    <row r="156" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:31" ht="15.75" thickBot="1">
       <c r="A156" s="41" t="s">
         <v>110</v>
       </c>
@@ -12545,7 +12535,7 @@
         <v>83.61781376609099</v>
       </c>
     </row>
-    <row r="157" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:31" ht="15.75" thickBot="1">
       <c r="A157" s="35" t="s">
         <v>110</v>
       </c>
@@ -12626,7 +12616,7 @@
         <v>83.61781376609099</v>
       </c>
     </row>
-    <row r="158" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:31" ht="15.75" thickBot="1">
       <c r="A158" s="41" t="s">
         <v>110</v>
       </c>
@@ -12707,7 +12697,7 @@
         <v>83.61781376609099</v>
       </c>
     </row>
-    <row r="159" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:31" ht="15.75" thickBot="1">
       <c r="A159" s="35" t="s">
         <v>110</v>
       </c>
@@ -12788,7 +12778,7 @@
         <v>83.61781376609099</v>
       </c>
     </row>
-    <row r="160" spans="1:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:31" ht="15.75" thickBot="1">
       <c r="A160" s="41" t="s">
         <v>110</v>
       </c>
@@ -12839,7 +12829,7 @@
       <c r="Z160" s="12"/>
       <c r="AA160" s="12"/>
     </row>
-    <row r="161" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:27" ht="15.75" thickBot="1">
       <c r="A161" s="35" t="s">
         <v>46</v>
       </c>
@@ -12890,7 +12880,7 @@
       <c r="Z161" s="12"/>
       <c r="AA161" s="12"/>
     </row>
-    <row r="162" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:27" ht="15.75" thickBot="1">
       <c r="A162" s="41" t="s">
         <v>46</v>
       </c>
@@ -12941,7 +12931,7 @@
       <c r="Z162" s="12"/>
       <c r="AA162" s="12"/>
     </row>
-    <row r="163" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:27" ht="15.75" thickBot="1">
       <c r="A163" s="35" t="s">
         <v>46</v>
       </c>
@@ -12992,7 +12982,7 @@
       <c r="Z163" s="12"/>
       <c r="AA163" s="12"/>
     </row>
-    <row r="164" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:27" ht="15.75" thickBot="1">
       <c r="A164" s="41" t="s">
         <v>46</v>
       </c>
@@ -13043,7 +13033,7 @@
       <c r="Z164" s="12"/>
       <c r="AA164" s="12"/>
     </row>
-    <row r="165" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:27" ht="15.75" thickBot="1">
       <c r="A165" s="35" t="s">
         <v>46</v>
       </c>
@@ -13094,7 +13084,7 @@
       <c r="Z165" s="12"/>
       <c r="AA165" s="12"/>
     </row>
-    <row r="166" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:27" ht="15.75" thickBot="1">
       <c r="A166" s="41" t="s">
         <v>46</v>
       </c>
@@ -13145,7 +13135,7 @@
       <c r="Z166" s="12"/>
       <c r="AA166" s="12"/>
     </row>
-    <row r="167" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:27" ht="15.75" thickBot="1">
       <c r="A167" s="35" t="s">
         <v>111</v>
       </c>
@@ -13196,7 +13186,7 @@
       <c r="Z167" s="12"/>
       <c r="AA167" s="12"/>
     </row>
-    <row r="168" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:27" ht="15.75" thickBot="1">
       <c r="A168" s="41" t="s">
         <v>111</v>
       </c>
@@ -13247,7 +13237,7 @@
       <c r="Z168" s="12"/>
       <c r="AA168" s="12"/>
     </row>
-    <row r="169" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:27" ht="15.75" thickBot="1">
       <c r="A169" s="35" t="s">
         <v>111</v>
       </c>
@@ -13298,7 +13288,7 @@
       <c r="Z169" s="12"/>
       <c r="AA169" s="12"/>
     </row>
-    <row r="170" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:27" ht="15.75" thickBot="1">
       <c r="A170" s="41" t="s">
         <v>111</v>
       </c>
@@ -13349,7 +13339,7 @@
       <c r="Z170" s="12"/>
       <c r="AA170" s="12"/>
     </row>
-    <row r="171" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:27" ht="15.75" thickBot="1">
       <c r="A171" s="35" t="s">
         <v>111</v>
       </c>
@@ -13400,7 +13390,7 @@
       <c r="Z171" s="12"/>
       <c r="AA171" s="12"/>
     </row>
-    <row r="172" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:27" ht="15.75" thickBot="1">
       <c r="A172" s="41" t="s">
         <v>111</v>
       </c>
@@ -13451,7 +13441,7 @@
       <c r="Z172" s="12"/>
       <c r="AA172" s="12"/>
     </row>
-    <row r="173" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:27" ht="15.75" thickBot="1">
       <c r="A173" s="68" t="s">
         <v>109</v>
       </c>
@@ -13493,7 +13483,7 @@
       <c r="Z173" s="12"/>
       <c r="AA173" s="12"/>
     </row>
-    <row r="174" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:27" ht="15.75" thickBot="1">
       <c r="A174" s="68" t="s">
         <v>110</v>
       </c>
@@ -13535,7 +13525,7 @@
       <c r="Z174" s="12"/>
       <c r="AA174" s="12"/>
     </row>
-    <row r="175" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:27" ht="15.75" thickBot="1">
       <c r="A175" s="68" t="s">
         <v>46</v>
       </c>
@@ -13577,7 +13567,7 @@
       <c r="Z175" s="12"/>
       <c r="AA175" s="12"/>
     </row>
-    <row r="176" spans="1:27" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:27" ht="15.75" thickBot="1">
       <c r="A176" s="68" t="s">
         <v>111</v>
       </c>
@@ -13619,7 +13609,7 @@
       <c r="Z176" s="12"/>
       <c r="AA176" s="12"/>
     </row>
-    <row r="177" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:27">
       <c r="A177" s="12"/>
       <c r="B177" s="12"/>
       <c r="C177" s="12"/>
@@ -13648,7 +13638,7 @@
       <c r="Z177" s="12"/>
       <c r="AA177" s="12"/>
     </row>
-    <row r="178" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:27">
       <c r="A178" s="12"/>
       <c r="B178" s="12"/>
       <c r="C178" s="12"/>
@@ -13677,7 +13667,7 @@
       <c r="Z178" s="12"/>
       <c r="AA178" s="12"/>
     </row>
-    <row r="179" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:27">
       <c r="A179" s="18" t="s">
         <v>137</v>
       </c>
@@ -13708,7 +13698,7 @@
       <c r="Z179" s="12"/>
       <c r="AA179" s="12"/>
     </row>
-    <row r="180" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:27">
       <c r="A180" s="12" t="s">
         <v>138</v>
       </c>
@@ -13771,7 +13761,7 @@
       <c r="Z180" s="12"/>
       <c r="AA180" s="12"/>
     </row>
-    <row r="181" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:27">
       <c r="A181" s="12" t="s">
         <v>139</v>
       </c>
@@ -13850,7 +13840,7 @@
       <c r="Z181" s="12"/>
       <c r="AA181" s="12"/>
     </row>
-    <row r="182" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:27">
       <c r="A182" s="12" t="s">
         <v>135</v>
       </c>
@@ -13929,7 +13919,7 @@
       <c r="Z182" s="12"/>
       <c r="AA182" s="12"/>
     </row>
-    <row r="183" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:27">
       <c r="A183" s="12"/>
       <c r="B183" s="12"/>
       <c r="C183" s="17"/>
@@ -13988,7 +13978,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D0E4120-3854-4EE1-9E42-CF63CA26AF1E}">
   <dimension ref="A1:AE372"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="40.140625" customWidth="1"/>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
@@ -13996,12 +13986,12 @@
     <col min="28" max="28" width="9.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:31">
       <c r="A1" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:31">
       <c r="B2">
         <v>2021</v>
       </c>
@@ -14093,7 +14083,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:31">
       <c r="A3" s="74" t="s">
         <v>217</v>
       </c>
@@ -14218,7 +14208,7 @@
         <v>130641797616</v>
       </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:31">
       <c r="A4">
         <v>3</v>
       </c>
@@ -14343,7 +14333,7 @@
         <v>123324758518</v>
       </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:31">
       <c r="A5">
         <v>4</v>
       </c>
@@ -14468,7 +14458,7 @@
         <v>22481978241</v>
       </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:31">
       <c r="A6">
         <v>5</v>
       </c>
@@ -14593,7 +14583,7 @@
         <v>34590984593</v>
       </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:31">
       <c r="A7">
         <v>6</v>
       </c>
@@ -14718,7 +14708,7 @@
         <v>27570635908</v>
       </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:31">
       <c r="A8">
         <v>7</v>
       </c>
@@ -14843,7 +14833,7 @@
         <v>19474802616</v>
       </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:31">
       <c r="A9">
         <v>8</v>
       </c>
@@ -14968,12 +14958,12 @@
         <v>185700776885</v>
       </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:31">
       <c r="A11" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:31">
       <c r="B12">
         <v>2021</v>
       </c>
@@ -15065,7 +15055,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:31">
       <c r="A13" t="s">
         <v>218</v>
       </c>
@@ -15190,7 +15180,7 @@
         <v>0.58604270197066977</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:31">
       <c r="A14" s="74" t="s">
         <v>219</v>
       </c>
@@ -15315,7 +15305,7 @@
         <v>9.4917741494206828E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:31">
       <c r="A15" s="74" t="s">
         <v>220</v>
       </c>
@@ -15440,23 +15430,23 @@
         <v>0.90508225850579316</v>
       </c>
     </row>
-    <row r="17" spans="1:30" s="95" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" s="95" customFormat="1" ht="15.75">
       <c r="A17" s="94" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30">
       <c r="A18" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30">
       <c r="H19" s="96"/>
       <c r="M19" s="96"/>
       <c r="P19" s="96"/>
       <c r="W19" s="96"/>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30">
       <c r="H20" s="97" t="s">
         <v>223</v>
       </c>
@@ -15480,7 +15470,7 @@
       <c r="V20" s="99"/>
       <c r="W20" s="96"/>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30">
       <c r="B21" t="s">
         <v>226</v>
       </c>
@@ -15554,7 +15544,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30">
       <c r="B22">
         <v>2012</v>
       </c>
@@ -15641,7 +15631,7 @@
         <v>269204.92893499997</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30">
       <c r="B23">
         <v>2012</v>
       </c>
@@ -15728,7 +15718,7 @@
         <v>275014.26959799998</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30">
       <c r="B24">
         <v>2012</v>
       </c>
@@ -15815,7 +15805,7 @@
         <v>279128.70267299999</v>
       </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30">
       <c r="B25">
         <v>2012</v>
       </c>
@@ -15902,7 +15892,7 @@
         <v>279838.554198</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30">
       <c r="B26">
         <v>2012</v>
       </c>
@@ -15989,7 +15979,7 @@
         <v>287889.96027500002</v>
       </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30">
       <c r="B27">
         <v>2012</v>
       </c>
@@ -16076,7 +16066,7 @@
         <v>297585.30382600002</v>
       </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30">
       <c r="B28">
         <v>2012</v>
       </c>
@@ -16163,7 +16153,7 @@
         <v>304857.04434000002</v>
       </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30">
       <c r="B29">
         <v>2012</v>
       </c>
@@ -16250,7 +16240,7 @@
         <v>300044.746866</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30">
       <c r="B30">
         <v>2012</v>
       </c>
@@ -16337,7 +16327,7 @@
         <v>302135.239413</v>
       </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30">
       <c r="B31">
         <v>2013</v>
       </c>
@@ -16425,7 +16415,7 @@
         <v>315286.512973</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30">
       <c r="B32">
         <v>2013</v>
       </c>
@@ -16513,7 +16503,7 @@
         <v>321947.05459299998</v>
       </c>
     </row>
-    <row r="33" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:30">
       <c r="B33">
         <v>2013</v>
       </c>
@@ -16601,7 +16591,7 @@
         <v>320699.79185600003</v>
       </c>
     </row>
-    <row r="34" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:30">
       <c r="B34">
         <v>2013</v>
       </c>
@@ -16689,7 +16679,7 @@
         <v>321099.69637999998</v>
       </c>
     </row>
-    <row r="35" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:30">
       <c r="B35">
         <v>2013</v>
       </c>
@@ -16777,7 +16767,7 @@
         <v>324016.78480200004</v>
       </c>
     </row>
-    <row r="36" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:30">
       <c r="B36">
         <v>2013</v>
       </c>
@@ -16865,7 +16855,7 @@
         <v>328476.361515</v>
       </c>
     </row>
-    <row r="37" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:30">
       <c r="B37">
         <v>2013</v>
       </c>
@@ -16953,7 +16943,7 @@
         <v>332291.28607899998</v>
       </c>
     </row>
-    <row r="38" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:30">
       <c r="B38">
         <v>2013</v>
       </c>
@@ -17041,7 +17031,7 @@
         <v>335752.19136</v>
       </c>
     </row>
-    <row r="39" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:30">
       <c r="B39">
         <v>2013</v>
       </c>
@@ -17129,7 +17119,7 @@
         <v>338568.93268099998</v>
       </c>
     </row>
-    <row r="40" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:30">
       <c r="B40">
         <v>2014</v>
       </c>
@@ -17217,7 +17207,7 @@
         <v>341094.03420599998</v>
       </c>
     </row>
-    <row r="41" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:30">
       <c r="B41">
         <v>2014</v>
       </c>
@@ -17305,7 +17295,7 @@
         <v>344130.233381</v>
       </c>
     </row>
-    <row r="42" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:30">
       <c r="B42">
         <v>2014</v>
       </c>
@@ -17393,7 +17383,7 @@
         <v>348243.08857100003</v>
       </c>
     </row>
-    <row r="43" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:30">
       <c r="B43">
         <v>2014</v>
       </c>
@@ -17481,7 +17471,7 @@
         <v>351625.99503300001</v>
       </c>
     </row>
-    <row r="44" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:30">
       <c r="B44">
         <v>2014</v>
       </c>
@@ -17569,7 +17559,7 @@
         <v>354872.73295999999</v>
       </c>
     </row>
-    <row r="45" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:30">
       <c r="B45">
         <v>2014</v>
       </c>
@@ -17657,7 +17647,7 @@
         <v>358367.67353300005</v>
       </c>
     </row>
-    <row r="46" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:30">
       <c r="B46">
         <v>2014</v>
       </c>
@@ -17745,7 +17735,7 @@
         <v>361320.58264000004</v>
       </c>
     </row>
-    <row r="47" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:30">
       <c r="B47">
         <v>2014</v>
       </c>
@@ -17833,7 +17823,7 @@
         <v>364871.36687600001</v>
       </c>
     </row>
-    <row r="48" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:30">
       <c r="B48">
         <v>2014</v>
       </c>
@@ -17921,7 +17911,7 @@
         <v>368410.84730599995</v>
       </c>
     </row>
-    <row r="49" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:30">
       <c r="B49">
         <v>2015</v>
       </c>
@@ -18009,7 +17999,7 @@
         <v>371886.64559299999</v>
       </c>
     </row>
-    <row r="50" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:30">
       <c r="B50">
         <v>2015</v>
       </c>
@@ -18097,7 +18087,7 @@
         <v>375662.94042900001</v>
       </c>
     </row>
-    <row r="51" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:30">
       <c r="B51">
         <v>2015</v>
       </c>
@@ -18185,7 +18175,7 @@
         <v>379485.037556</v>
       </c>
     </row>
-    <row r="52" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:30">
       <c r="B52">
         <v>2015</v>
       </c>
@@ -18273,7 +18263,7 @@
         <v>383492.49935100001</v>
       </c>
     </row>
-    <row r="53" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:30">
       <c r="B53">
         <v>2015</v>
       </c>
@@ -18361,7 +18351,7 @@
         <v>387363.04502800002</v>
       </c>
     </row>
-    <row r="54" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:30">
       <c r="B54">
         <v>2015</v>
       </c>
@@ -18449,7 +18439,7 @@
         <v>390923.53863600001</v>
       </c>
     </row>
-    <row r="55" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:30">
       <c r="B55">
         <v>2015</v>
       </c>
@@ -18537,7 +18527,7 @@
         <v>394061.25975500001</v>
       </c>
     </row>
-    <row r="56" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:30">
       <c r="B56">
         <v>2015</v>
       </c>
@@ -18625,7 +18615,7 @@
         <v>397535.01028799999</v>
       </c>
     </row>
-    <row r="57" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:30">
       <c r="B57">
         <v>2015</v>
       </c>
@@ -18713,7 +18703,7 @@
         <v>401206.37462900003</v>
       </c>
     </row>
-    <row r="58" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:30">
       <c r="B58">
         <v>2016</v>
       </c>
@@ -18801,7 +18791,7 @@
         <v>404637.34415300004</v>
       </c>
     </row>
-    <row r="59" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:30">
       <c r="B59">
         <v>2016</v>
       </c>
@@ -18889,7 +18879,7 @@
         <v>408336.174405</v>
       </c>
     </row>
-    <row r="60" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:30">
       <c r="B60">
         <v>2016</v>
       </c>
@@ -18977,7 +18967,7 @@
         <v>413143.93676100002</v>
       </c>
     </row>
-    <row r="61" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:30">
       <c r="B61">
         <v>2016</v>
       </c>
@@ -19046,7 +19036,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:30">
       <c r="B62">
         <v>2016</v>
       </c>
@@ -19115,7 +19105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:30">
       <c r="B63">
         <v>2016</v>
       </c>
@@ -19184,7 +19174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="2:30" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:30">
       <c r="B64">
         <v>2016</v>
       </c>
@@ -19253,7 +19243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:23">
       <c r="B65">
         <v>2016</v>
       </c>
@@ -19322,7 +19312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:23">
       <c r="B66">
         <v>2016</v>
       </c>
@@ -19391,7 +19381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:23">
       <c r="B67">
         <v>2017</v>
       </c>
@@ -19460,7 +19450,7 @@
         <v>6775192</v>
       </c>
     </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:23">
       <c r="B68">
         <v>2017</v>
       </c>
@@ -19529,7 +19519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:23">
       <c r="B69">
         <v>2017</v>
       </c>
@@ -19598,7 +19588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:23">
       <c r="B70">
         <v>2017</v>
       </c>
@@ -19667,7 +19657,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:23">
       <c r="B71">
         <v>2017</v>
       </c>
@@ -19736,7 +19726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:23">
       <c r="B72">
         <v>2017</v>
       </c>
@@ -19805,7 +19795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:23">
       <c r="B73">
         <v>2017</v>
       </c>
@@ -19874,7 +19864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:23">
       <c r="B74">
         <v>2017</v>
       </c>
@@ -19943,7 +19933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:23">
       <c r="B75">
         <v>2017</v>
       </c>
@@ -20012,7 +20002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:23">
       <c r="B76">
         <v>2018</v>
       </c>
@@ -20081,7 +20071,7 @@
         <v>6854305</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:23">
       <c r="B77">
         <v>2018</v>
       </c>
@@ -20150,7 +20140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:23">
       <c r="B78">
         <v>2018</v>
       </c>
@@ -20216,7 +20206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:23">
       <c r="B79">
         <v>2018</v>
       </c>
@@ -20285,7 +20275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:23">
       <c r="B80">
         <v>2018</v>
       </c>
@@ -20354,7 +20344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:23">
       <c r="B81">
         <v>2018</v>
       </c>
@@ -20423,7 +20413,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:23">
       <c r="B82">
         <v>2018</v>
       </c>
@@ -20492,7 +20482,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:23">
       <c r="B83">
         <v>2018</v>
       </c>
@@ -20561,7 +20551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:23">
       <c r="B84">
         <v>2018</v>
       </c>
@@ -20630,7 +20620,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:23">
       <c r="B85">
         <v>2019</v>
       </c>
@@ -20699,7 +20689,7 @@
         <v>6500376</v>
       </c>
     </row>
-    <row r="86" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:23">
       <c r="B86">
         <v>2019</v>
       </c>
@@ -20768,7 +20758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:23">
       <c r="B87">
         <v>2019</v>
       </c>
@@ -20837,7 +20827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:23">
       <c r="B88">
         <v>2019</v>
       </c>
@@ -20906,7 +20896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:23">
       <c r="B89">
         <v>2019</v>
       </c>
@@ -20975,7 +20965,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:23">
       <c r="B90">
         <v>2019</v>
       </c>
@@ -21044,7 +21034,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:23">
       <c r="B91">
         <v>2019</v>
       </c>
@@ -21113,7 +21103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:23">
       <c r="B92">
         <v>2019</v>
       </c>
@@ -21182,7 +21172,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:23">
       <c r="B93">
         <v>2019</v>
       </c>
@@ -21251,7 +21241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:23">
       <c r="B94">
         <v>2020</v>
       </c>
@@ -21320,7 +21310,7 @@
         <v>5911418</v>
       </c>
     </row>
-    <row r="95" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:23">
       <c r="B95">
         <v>2020</v>
       </c>
@@ -21389,7 +21379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:23">
       <c r="B96">
         <v>2020</v>
       </c>
@@ -21458,7 +21448,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:23">
       <c r="B97">
         <v>2020</v>
       </c>
@@ -21527,7 +21517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:23">
       <c r="B98">
         <v>2020</v>
       </c>
@@ -21596,7 +21586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:23">
       <c r="B99">
         <v>2020</v>
       </c>
@@ -21665,7 +21655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:23">
       <c r="B100">
         <v>2020</v>
       </c>
@@ -21734,7 +21724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:23">
       <c r="B101">
         <v>2020</v>
       </c>
@@ -21803,7 +21793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:23">
       <c r="B102">
         <v>2020</v>
       </c>
@@ -21872,7 +21862,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:23">
       <c r="B103">
         <v>2021</v>
       </c>
@@ -21941,7 +21931,7 @@
         <v>7145296</v>
       </c>
     </row>
-    <row r="104" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:23">
       <c r="B104">
         <v>2021</v>
       </c>
@@ -22010,7 +22000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:23">
       <c r="B105">
         <v>2021</v>
       </c>
@@ -22079,7 +22069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:23">
       <c r="B106">
         <v>2021</v>
       </c>
@@ -22148,7 +22138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:23">
       <c r="B107">
         <v>2021</v>
       </c>
@@ -22217,7 +22207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:23">
       <c r="B108">
         <v>2021</v>
       </c>
@@ -22286,7 +22276,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:23">
       <c r="B109">
         <v>2021</v>
       </c>
@@ -22355,7 +22345,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:23">
       <c r="B110">
         <v>2021</v>
       </c>
@@ -22424,7 +22414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:23">
       <c r="B111">
         <v>2021</v>
       </c>
@@ -22493,7 +22483,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:23">
       <c r="B112">
         <v>2022</v>
       </c>
@@ -22562,7 +22552,7 @@
         <v>7899190</v>
       </c>
     </row>
-    <row r="113" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:23">
       <c r="B113">
         <v>2022</v>
       </c>
@@ -22631,7 +22621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:23">
       <c r="B114">
         <v>2022</v>
       </c>
@@ -22700,7 +22690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:23">
       <c r="B115">
         <v>2022</v>
       </c>
@@ -22769,7 +22759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:23">
       <c r="B116">
         <v>2022</v>
       </c>
@@ -22838,7 +22828,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:23">
       <c r="B117">
         <v>2022</v>
       </c>
@@ -22907,7 +22897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:23">
       <c r="B118">
         <v>2022</v>
       </c>
@@ -22976,7 +22966,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:23">
       <c r="B119">
         <v>2022</v>
       </c>
@@ -23045,7 +23035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:23">
       <c r="B120">
         <v>2022</v>
       </c>
@@ -23114,7 +23104,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:23">
       <c r="B121">
         <v>2023</v>
       </c>
@@ -23183,7 +23173,7 @@
         <v>8510344</v>
       </c>
     </row>
-    <row r="122" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:23">
       <c r="B122">
         <v>2023</v>
       </c>
@@ -23252,7 +23242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:23">
       <c r="B123">
         <v>2023</v>
       </c>
@@ -23321,7 +23311,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:23">
       <c r="B124">
         <v>2023</v>
       </c>
@@ -23390,7 +23380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:23">
       <c r="B125">
         <v>2023</v>
       </c>
@@ -23459,7 +23449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:23">
       <c r="B126">
         <v>2023</v>
       </c>
@@ -23528,7 +23518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:23">
       <c r="B127">
         <v>2023</v>
       </c>
@@ -23597,7 +23587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:23">
       <c r="B128">
         <v>2023</v>
       </c>
@@ -23666,7 +23656,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:23">
       <c r="B129">
         <v>2023</v>
       </c>
@@ -23735,7 +23725,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:23">
       <c r="B130">
         <v>2024</v>
       </c>
@@ -23804,7 +23794,7 @@
         <v>9126118</v>
       </c>
     </row>
-    <row r="131" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:23">
       <c r="B131">
         <v>2024</v>
       </c>
@@ -23873,7 +23863,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:23">
       <c r="B132">
         <v>2024</v>
       </c>
@@ -23942,7 +23932,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:23">
       <c r="B133">
         <v>2024</v>
       </c>
@@ -24011,7 +24001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:23">
       <c r="B134">
         <v>2024</v>
       </c>
@@ -24080,7 +24070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:23">
       <c r="B135">
         <v>2024</v>
       </c>
@@ -24149,7 +24139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:23">
       <c r="B136">
         <v>2024</v>
       </c>
@@ -24218,7 +24208,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:23">
       <c r="B137">
         <v>2024</v>
       </c>
@@ -24287,7 +24277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:23">
       <c r="B138">
         <v>2024</v>
       </c>
@@ -24356,7 +24346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:23">
       <c r="B139">
         <v>2025</v>
       </c>
@@ -24425,7 +24415,7 @@
         <v>9739533</v>
       </c>
     </row>
-    <row r="140" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:23">
       <c r="B140">
         <v>2025</v>
       </c>
@@ -24494,7 +24484,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:23">
       <c r="B141">
         <v>2025</v>
       </c>
@@ -24563,7 +24553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:23">
       <c r="B142">
         <v>2025</v>
       </c>
@@ -24632,7 +24622,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:23">
       <c r="B143">
         <v>2025</v>
       </c>
@@ -24701,7 +24691,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:23">
       <c r="B144">
         <v>2025</v>
       </c>
@@ -24770,7 +24760,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:23">
       <c r="B145">
         <v>2025</v>
       </c>
@@ -24839,7 +24829,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:23">
       <c r="B146">
         <v>2025</v>
       </c>
@@ -24908,7 +24898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:23">
       <c r="B147">
         <v>2025</v>
       </c>
@@ -24977,7 +24967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:23">
       <c r="B148">
         <v>2026</v>
       </c>
@@ -25046,7 +25036,7 @@
         <v>10316053</v>
       </c>
     </row>
-    <row r="149" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:23">
       <c r="B149">
         <v>2026</v>
       </c>
@@ -25115,7 +25105,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:23">
       <c r="B150">
         <v>2026</v>
       </c>
@@ -25184,7 +25174,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:23">
       <c r="B151">
         <v>2026</v>
       </c>
@@ -25253,7 +25243,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:23">
       <c r="B152">
         <v>2026</v>
       </c>
@@ -25322,7 +25312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:23">
       <c r="B153">
         <v>2026</v>
       </c>
@@ -25391,7 +25381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:23">
       <c r="B154">
         <v>2026</v>
       </c>
@@ -25460,7 +25450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:23">
       <c r="B155">
         <v>2026</v>
       </c>
@@ -25529,7 +25519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:23">
       <c r="B156">
         <v>2026</v>
       </c>
@@ -25598,7 +25588,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:23">
       <c r="B157">
         <v>2027</v>
       </c>
@@ -25667,7 +25657,7 @@
         <v>10792452</v>
       </c>
     </row>
-    <row r="158" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:23">
       <c r="B158">
         <v>2027</v>
       </c>
@@ -25736,7 +25726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:23">
       <c r="B159">
         <v>2027</v>
       </c>
@@ -25805,7 +25795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:23">
       <c r="B160">
         <v>2027</v>
       </c>
@@ -25874,7 +25864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:23">
       <c r="B161">
         <v>2027</v>
       </c>
@@ -25943,7 +25933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:23">
       <c r="B162">
         <v>2027</v>
       </c>
@@ -26012,7 +26002,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:23">
       <c r="B163">
         <v>2027</v>
       </c>
@@ -26081,7 +26071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:23">
       <c r="B164">
         <v>2027</v>
       </c>
@@ -26150,7 +26140,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:23">
       <c r="B165">
         <v>2027</v>
       </c>
@@ -26219,7 +26209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:23">
       <c r="B166">
         <v>2028</v>
       </c>
@@ -26288,7 +26278,7 @@
         <v>11176272</v>
       </c>
     </row>
-    <row r="167" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:23">
       <c r="B167">
         <v>2028</v>
       </c>
@@ -26357,7 +26347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:23">
       <c r="B168">
         <v>2028</v>
       </c>
@@ -26426,7 +26416,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:23">
       <c r="B169">
         <v>2028</v>
       </c>
@@ -26495,7 +26485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:23">
       <c r="B170">
         <v>2028</v>
       </c>
@@ -26564,7 +26554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:23">
       <c r="B171">
         <v>2028</v>
       </c>
@@ -26633,7 +26623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:23">
       <c r="B172">
         <v>2028</v>
       </c>
@@ -26702,7 +26692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:23">
       <c r="B173">
         <v>2028</v>
       </c>
@@ -26771,7 +26761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:23">
       <c r="B174">
         <v>2028</v>
       </c>
@@ -26840,7 +26830,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:23">
       <c r="B175">
         <v>2029</v>
       </c>
@@ -26909,7 +26899,7 @@
         <v>11474709</v>
       </c>
     </row>
-    <row r="176" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:23">
       <c r="B176">
         <v>2029</v>
       </c>
@@ -26978,7 +26968,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:23">
       <c r="B177">
         <v>2029</v>
       </c>
@@ -27047,7 +27037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:23">
       <c r="B178">
         <v>2029</v>
       </c>
@@ -27116,7 +27106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:23">
       <c r="B179">
         <v>2029</v>
       </c>
@@ -27185,7 +27175,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:23">
       <c r="B180">
         <v>2029</v>
       </c>
@@ -27254,7 +27244,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:23">
       <c r="B181">
         <v>2029</v>
       </c>
@@ -27323,7 +27313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:23">
       <c r="B182">
         <v>2029</v>
       </c>
@@ -27392,7 +27382,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:23">
       <c r="B183">
         <v>2029</v>
       </c>
@@ -27461,7 +27451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:23">
       <c r="B184">
         <v>2030</v>
       </c>
@@ -27530,7 +27520,7 @@
         <v>11718101</v>
       </c>
     </row>
-    <row r="185" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:23">
       <c r="B185">
         <v>2030</v>
       </c>
@@ -27599,7 +27589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:23">
       <c r="B186">
         <v>2030</v>
       </c>
@@ -27668,7 +27658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:23">
       <c r="B187">
         <v>2030</v>
       </c>
@@ -27737,7 +27727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:23">
       <c r="B188">
         <v>2030</v>
       </c>
@@ -27806,7 +27796,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:23">
       <c r="B189">
         <v>2030</v>
       </c>
@@ -27875,7 +27865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:23">
       <c r="B190">
         <v>2030</v>
       </c>
@@ -27944,7 +27934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:23">
       <c r="B191">
         <v>2030</v>
       </c>
@@ -28013,7 +28003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:23">
       <c r="B192">
         <v>2030</v>
       </c>
@@ -28082,7 +28072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:23">
       <c r="B193">
         <v>2031</v>
       </c>
@@ -28151,7 +28141,7 @@
         <v>11950609</v>
       </c>
     </row>
-    <row r="194" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:23">
       <c r="B194">
         <v>2031</v>
       </c>
@@ -28220,7 +28210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:23">
       <c r="B195">
         <v>2031</v>
       </c>
@@ -28289,7 +28279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:23">
       <c r="B196">
         <v>2031</v>
       </c>
@@ -28358,7 +28348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:23">
       <c r="B197">
         <v>2031</v>
       </c>
@@ -28427,7 +28417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:23">
       <c r="B198">
         <v>2031</v>
       </c>
@@ -28496,7 +28486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:23">
       <c r="B199">
         <v>2031</v>
       </c>
@@ -28565,7 +28555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:23">
       <c r="B200">
         <v>2031</v>
       </c>
@@ -28634,7 +28624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:23">
       <c r="B201">
         <v>2031</v>
       </c>
@@ -28703,7 +28693,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:23">
       <c r="B202">
         <v>2032</v>
       </c>
@@ -28772,7 +28762,7 @@
         <v>12202189</v>
       </c>
     </row>
-    <row r="203" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:23">
       <c r="B203">
         <v>2032</v>
       </c>
@@ -28841,7 +28831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:23">
       <c r="B204">
         <v>2032</v>
       </c>
@@ -28910,7 +28900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:23">
       <c r="B205">
         <v>2032</v>
       </c>
@@ -28979,7 +28969,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:23">
       <c r="B206">
         <v>2032</v>
       </c>
@@ -29048,7 +29038,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:23">
       <c r="B207">
         <v>2032</v>
       </c>
@@ -29117,7 +29107,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:23">
       <c r="B208">
         <v>2032</v>
       </c>
@@ -29186,7 +29176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:23">
       <c r="B209">
         <v>2032</v>
       </c>
@@ -29255,7 +29245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:23">
       <c r="B210">
         <v>2032</v>
       </c>
@@ -29324,7 +29314,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:23">
       <c r="B211">
         <v>2033</v>
       </c>
@@ -29393,7 +29383,7 @@
         <v>12426002</v>
       </c>
     </row>
-    <row r="212" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:23">
       <c r="B212">
         <v>2033</v>
       </c>
@@ -29462,7 +29452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:23">
       <c r="B213">
         <v>2033</v>
       </c>
@@ -29531,7 +29521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:23">
       <c r="B214">
         <v>2033</v>
       </c>
@@ -29600,7 +29590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:23">
       <c r="B215">
         <v>2033</v>
       </c>
@@ -29669,7 +29659,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="216" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:23">
       <c r="B216">
         <v>2033</v>
       </c>
@@ -29738,7 +29728,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:23">
       <c r="B217">
         <v>2033</v>
       </c>
@@ -29807,7 +29797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:23">
       <c r="B218">
         <v>2033</v>
       </c>
@@ -29876,7 +29866,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:23">
       <c r="B219">
         <v>2033</v>
       </c>
@@ -29945,7 +29935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:23">
       <c r="B220">
         <v>2034</v>
       </c>
@@ -30014,7 +30004,7 @@
         <v>12642420</v>
       </c>
     </row>
-    <row r="221" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:23">
       <c r="B221">
         <v>2034</v>
       </c>
@@ -30083,7 +30073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:23">
       <c r="B222">
         <v>2034</v>
       </c>
@@ -30152,7 +30142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:23">
       <c r="B223">
         <v>2034</v>
       </c>
@@ -30221,7 +30211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="224" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:23">
       <c r="B224">
         <v>2034</v>
       </c>
@@ -30290,7 +30280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="225" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:23">
       <c r="B225">
         <v>2034</v>
       </c>
@@ -30359,7 +30349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="226" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:23">
       <c r="B226">
         <v>2034</v>
       </c>
@@ -30428,7 +30418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="227" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:23">
       <c r="B227">
         <v>2034</v>
       </c>
@@ -30497,7 +30487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="228" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:23">
       <c r="B228">
         <v>2034</v>
       </c>
@@ -30566,7 +30556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="229" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:23">
       <c r="B229">
         <v>2035</v>
       </c>
@@ -30635,7 +30625,7 @@
         <v>12841677</v>
       </c>
     </row>
-    <row r="230" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:23">
       <c r="B230">
         <v>2035</v>
       </c>
@@ -30704,7 +30694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="231" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:23">
       <c r="B231">
         <v>2035</v>
       </c>
@@ -30773,7 +30763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="232" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:23">
       <c r="B232">
         <v>2035</v>
       </c>
@@ -30842,7 +30832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="233" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:23">
       <c r="B233">
         <v>2035</v>
       </c>
@@ -30911,7 +30901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="234" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:23">
       <c r="B234">
         <v>2035</v>
       </c>
@@ -30980,7 +30970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="235" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:23">
       <c r="B235">
         <v>2035</v>
       </c>
@@ -31049,7 +31039,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="236" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:23">
       <c r="B236">
         <v>2035</v>
       </c>
@@ -31118,7 +31108,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="237" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:23">
       <c r="B237">
         <v>2035</v>
       </c>
@@ -31187,7 +31177,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="238" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:23">
       <c r="B238">
         <v>2036</v>
       </c>
@@ -31256,7 +31246,7 @@
         <v>12991660</v>
       </c>
     </row>
-    <row r="239" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:23">
       <c r="B239">
         <v>2036</v>
       </c>
@@ -31325,7 +31315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="240" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:23">
       <c r="B240">
         <v>2036</v>
       </c>
@@ -31394,7 +31384,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:23">
       <c r="B241">
         <v>2036</v>
       </c>
@@ -31463,7 +31453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:23">
       <c r="B242">
         <v>2036</v>
       </c>
@@ -31532,7 +31522,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:23">
       <c r="B243">
         <v>2036</v>
       </c>
@@ -31601,7 +31591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:23">
       <c r="B244">
         <v>2036</v>
       </c>
@@ -31670,7 +31660,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:23">
       <c r="B245">
         <v>2036</v>
       </c>
@@ -31739,7 +31729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:23">
       <c r="B246">
         <v>2036</v>
       </c>
@@ -31808,7 +31798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:23">
       <c r="B247">
         <v>2037</v>
       </c>
@@ -31877,7 +31867,7 @@
         <v>13129167</v>
       </c>
     </row>
-    <row r="248" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:23">
       <c r="B248">
         <v>2037</v>
       </c>
@@ -31946,7 +31936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="249" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:23">
       <c r="B249">
         <v>2037</v>
       </c>
@@ -32015,7 +32005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:23">
       <c r="B250">
         <v>2037</v>
       </c>
@@ -32084,7 +32074,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:23">
       <c r="B251">
         <v>2037</v>
       </c>
@@ -32153,7 +32143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:23">
       <c r="B252">
         <v>2037</v>
       </c>
@@ -32222,7 +32212,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:23">
       <c r="B253">
         <v>2037</v>
       </c>
@@ -32291,7 +32281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:23">
       <c r="B254">
         <v>2037</v>
       </c>
@@ -32360,7 +32350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="255" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:23">
       <c r="B255">
         <v>2037</v>
       </c>
@@ -32429,7 +32419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="256" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:23">
       <c r="B256">
         <v>2038</v>
       </c>
@@ -32498,7 +32488,7 @@
         <v>13234496</v>
       </c>
     </row>
-    <row r="257" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:23">
       <c r="B257">
         <v>2038</v>
       </c>
@@ -32567,7 +32557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="258" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:23">
       <c r="B258">
         <v>2038</v>
       </c>
@@ -32636,7 +32626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="259" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:23">
       <c r="B259">
         <v>2038</v>
       </c>
@@ -32705,7 +32695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="260" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:23">
       <c r="B260">
         <v>2038</v>
       </c>
@@ -32774,7 +32764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="261" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:23">
       <c r="B261">
         <v>2038</v>
       </c>
@@ -32843,7 +32833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="262" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:23">
       <c r="B262">
         <v>2038</v>
       </c>
@@ -32912,7 +32902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="263" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:23">
       <c r="B263">
         <v>2038</v>
       </c>
@@ -32981,7 +32971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="264" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:23">
       <c r="B264">
         <v>2038</v>
       </c>
@@ -33050,7 +33040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="265" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:23">
       <c r="B265">
         <v>2039</v>
       </c>
@@ -33119,7 +33109,7 @@
         <v>13310591</v>
       </c>
     </row>
-    <row r="266" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:23">
       <c r="B266">
         <v>2039</v>
       </c>
@@ -33188,7 +33178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="267" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:23">
       <c r="B267">
         <v>2039</v>
       </c>
@@ -33257,7 +33247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="268" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:23">
       <c r="B268">
         <v>2039</v>
       </c>
@@ -33326,7 +33316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="269" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:23">
       <c r="B269">
         <v>2039</v>
       </c>
@@ -33395,7 +33385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:23">
       <c r="B270">
         <v>2039</v>
       </c>
@@ -33464,7 +33454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:23">
       <c r="B271">
         <v>2039</v>
       </c>
@@ -33533,7 +33523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:23">
       <c r="B272">
         <v>2039</v>
       </c>
@@ -33602,7 +33592,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="273" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:23">
       <c r="B273">
         <v>2039</v>
       </c>
@@ -33671,7 +33661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="274" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:23">
       <c r="B274">
         <v>2040</v>
       </c>
@@ -33740,7 +33730,7 @@
         <v>13386520</v>
       </c>
     </row>
-    <row r="275" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:23">
       <c r="B275">
         <v>2040</v>
       </c>
@@ -33809,7 +33799,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:23">
       <c r="B276">
         <v>2040</v>
       </c>
@@ -33878,7 +33868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="277" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:23">
       <c r="B277">
         <v>2040</v>
       </c>
@@ -33947,7 +33937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="278" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:23">
       <c r="B278">
         <v>2040</v>
       </c>
@@ -34016,7 +34006,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:23">
       <c r="B279">
         <v>2040</v>
       </c>
@@ -34085,7 +34075,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:23">
       <c r="B280">
         <v>2040</v>
       </c>
@@ -34154,7 +34144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:23">
       <c r="B281">
         <v>2040</v>
       </c>
@@ -34223,7 +34213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:23">
       <c r="B282">
         <v>2040</v>
       </c>
@@ -34292,7 +34282,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:23">
       <c r="B283">
         <v>2041</v>
       </c>
@@ -34361,7 +34351,7 @@
         <v>13460125</v>
       </c>
     </row>
-    <row r="284" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:23">
       <c r="B284">
         <v>2041</v>
       </c>
@@ -34430,7 +34420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="285" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:23">
       <c r="B285">
         <v>2041</v>
       </c>
@@ -34499,7 +34489,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="286" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:23">
       <c r="B286">
         <v>2041</v>
       </c>
@@ -34568,7 +34558,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="287" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:23">
       <c r="B287">
         <v>2041</v>
       </c>
@@ -34637,7 +34627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="288" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:23">
       <c r="B288">
         <v>2041</v>
       </c>
@@ -34706,7 +34696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="289" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:23">
       <c r="B289">
         <v>2041</v>
       </c>
@@ -34775,7 +34765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="290" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:23">
       <c r="B290">
         <v>2041</v>
       </c>
@@ -34844,7 +34834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="291" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:23">
       <c r="B291">
         <v>2041</v>
       </c>
@@ -34913,7 +34903,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="292" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:23">
       <c r="B292">
         <v>2042</v>
       </c>
@@ -34982,7 +34972,7 @@
         <v>13537213</v>
       </c>
     </row>
-    <row r="293" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:23">
       <c r="B293">
         <v>2042</v>
       </c>
@@ -35051,7 +35041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="294" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:23">
       <c r="B294">
         <v>2042</v>
       </c>
@@ -35120,7 +35110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="295" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:23">
       <c r="B295">
         <v>2042</v>
       </c>
@@ -35189,7 +35179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="296" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:23">
       <c r="B296">
         <v>2042</v>
       </c>
@@ -35258,7 +35248,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="297" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:23">
       <c r="B297">
         <v>2042</v>
       </c>
@@ -35327,7 +35317,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="298" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:23">
       <c r="B298">
         <v>2042</v>
       </c>
@@ -35396,7 +35386,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:23">
       <c r="B299">
         <v>2042</v>
       </c>
@@ -35465,7 +35455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:23">
       <c r="B300">
         <v>2042</v>
       </c>
@@ -35534,7 +35524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:23">
       <c r="B301">
         <v>2043</v>
       </c>
@@ -35603,7 +35593,7 @@
         <v>13610875</v>
       </c>
     </row>
-    <row r="302" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:23">
       <c r="B302">
         <v>2043</v>
       </c>
@@ -35672,7 +35662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="303" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:23">
       <c r="B303">
         <v>2043</v>
       </c>
@@ -35741,7 +35731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="304" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:23">
       <c r="B304">
         <v>2043</v>
       </c>
@@ -35810,7 +35800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:23">
       <c r="B305">
         <v>2043</v>
       </c>
@@ -35879,7 +35869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="306" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:23">
       <c r="B306">
         <v>2043</v>
       </c>
@@ -35948,7 +35938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="307" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:23">
       <c r="B307">
         <v>2043</v>
       </c>
@@ -36017,7 +36007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:23">
       <c r="B308">
         <v>2043</v>
       </c>
@@ -36086,7 +36076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:23">
       <c r="B309">
         <v>2043</v>
       </c>
@@ -36155,7 +36145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:23">
       <c r="B310">
         <v>2044</v>
       </c>
@@ -36224,7 +36214,7 @@
         <v>13671004</v>
       </c>
     </row>
-    <row r="311" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:23">
       <c r="B311">
         <v>2044</v>
       </c>
@@ -36293,7 +36283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:23">
       <c r="B312">
         <v>2044</v>
       </c>
@@ -36362,7 +36352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="313" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:23">
       <c r="B313">
         <v>2044</v>
       </c>
@@ -36431,7 +36421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="314" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:23">
       <c r="B314">
         <v>2044</v>
       </c>
@@ -36500,7 +36490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="315" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:23">
       <c r="B315">
         <v>2044</v>
       </c>
@@ -36569,7 +36559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="316" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:23">
       <c r="B316">
         <v>2044</v>
       </c>
@@ -36638,7 +36628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="317" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:23">
       <c r="B317">
         <v>2044</v>
       </c>
@@ -36707,7 +36697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="318" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:23">
       <c r="B318">
         <v>2044</v>
       </c>
@@ -36776,7 +36766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="319" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:23">
       <c r="B319">
         <v>2045</v>
       </c>
@@ -36845,7 +36835,7 @@
         <v>13698105</v>
       </c>
     </row>
-    <row r="320" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:23">
       <c r="B320">
         <v>2045</v>
       </c>
@@ -36914,7 +36904,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="321" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:23">
       <c r="B321">
         <v>2045</v>
       </c>
@@ -36983,7 +36973,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="322" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:23">
       <c r="B322">
         <v>2045</v>
       </c>
@@ -37052,7 +37042,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="323" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:23">
       <c r="B323">
         <v>2045</v>
       </c>
@@ -37121,7 +37111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="324" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:23">
       <c r="B324">
         <v>2045</v>
       </c>
@@ -37190,7 +37180,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="325" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:23">
       <c r="B325">
         <v>2045</v>
       </c>
@@ -37259,7 +37249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="326" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:23">
       <c r="B326">
         <v>2045</v>
       </c>
@@ -37328,7 +37318,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="327" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:23">
       <c r="B327">
         <v>2045</v>
       </c>
@@ -37397,7 +37387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:23">
       <c r="B328">
         <v>2046</v>
       </c>
@@ -37466,7 +37456,7 @@
         <v>13712468</v>
       </c>
     </row>
-    <row r="329" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:23">
       <c r="B329">
         <v>2046</v>
       </c>
@@ -37535,7 +37525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:23">
       <c r="B330">
         <v>2046</v>
       </c>
@@ -37604,7 +37594,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="331" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:23">
       <c r="B331">
         <v>2046</v>
       </c>
@@ -37673,7 +37663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="332" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:23">
       <c r="B332">
         <v>2046</v>
       </c>
@@ -37742,7 +37732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="333" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:23">
       <c r="B333">
         <v>2046</v>
       </c>
@@ -37811,7 +37801,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:23">
       <c r="B334">
         <v>2046</v>
       </c>
@@ -37880,7 +37870,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:23">
       <c r="B335">
         <v>2046</v>
       </c>
@@ -37949,7 +37939,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:23">
       <c r="B336">
         <v>2046</v>
       </c>
@@ -38018,7 +38008,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:23">
       <c r="B337">
         <v>2047</v>
       </c>
@@ -38087,7 +38077,7 @@
         <v>13729347</v>
       </c>
     </row>
-    <row r="338" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:23">
       <c r="B338">
         <v>2047</v>
       </c>
@@ -38156,7 +38146,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:23">
       <c r="B339">
         <v>2047</v>
       </c>
@@ -38225,7 +38215,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:23">
       <c r="B340">
         <v>2047</v>
       </c>
@@ -38294,7 +38284,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:23">
       <c r="B341">
         <v>2047</v>
       </c>
@@ -38363,7 +38353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="342" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:23">
       <c r="B342">
         <v>2047</v>
       </c>
@@ -38432,7 +38422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="343" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:23">
       <c r="B343">
         <v>2047</v>
       </c>
@@ -38501,7 +38491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="344" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:23">
       <c r="B344">
         <v>2047</v>
       </c>
@@ -38570,7 +38560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="345" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:23">
       <c r="B345">
         <v>2047</v>
       </c>
@@ -38639,7 +38629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="346" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:23">
       <c r="B346">
         <v>2048</v>
       </c>
@@ -38708,7 +38698,7 @@
         <v>13744756</v>
       </c>
     </row>
-    <row r="347" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:23">
       <c r="B347">
         <v>2048</v>
       </c>
@@ -38777,7 +38767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="348" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:23">
       <c r="B348">
         <v>2048</v>
       </c>
@@ -38846,7 +38836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="349" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:23">
       <c r="B349">
         <v>2048</v>
       </c>
@@ -38915,7 +38905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="350" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:23">
       <c r="B350">
         <v>2048</v>
       </c>
@@ -38984,7 +38974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="351" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:23">
       <c r="B351">
         <v>2048</v>
       </c>
@@ -39053,7 +39043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="352" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:23">
       <c r="B352">
         <v>2048</v>
       </c>
@@ -39122,7 +39112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="353" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:23">
       <c r="B353">
         <v>2048</v>
       </c>
@@ -39191,7 +39181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="354" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:23">
       <c r="B354">
         <v>2048</v>
       </c>
@@ -39260,7 +39250,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="355" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:23">
       <c r="B355">
         <v>2049</v>
       </c>
@@ -39329,7 +39319,7 @@
         <v>13758281</v>
       </c>
     </row>
-    <row r="356" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:23">
       <c r="B356">
         <v>2049</v>
       </c>
@@ -39398,7 +39388,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:23">
       <c r="B357">
         <v>2049</v>
       </c>
@@ -39467,7 +39457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:23">
       <c r="B358">
         <v>2049</v>
       </c>
@@ -39536,7 +39526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:23">
       <c r="B359">
         <v>2049</v>
       </c>
@@ -39605,7 +39595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="360" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:23">
       <c r="B360">
         <v>2049</v>
       </c>
@@ -39674,7 +39664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="361" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:23">
       <c r="B361">
         <v>2049</v>
       </c>
@@ -39743,7 +39733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="362" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:23">
       <c r="B362">
         <v>2049</v>
       </c>
@@ -39812,7 +39802,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:23">
       <c r="B363">
         <v>2049</v>
       </c>
@@ -39881,7 +39871,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="364" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:23">
       <c r="B364">
         <v>2050</v>
       </c>
@@ -39950,7 +39940,7 @@
         <v>13817684</v>
       </c>
     </row>
-    <row r="365" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:23">
       <c r="B365">
         <v>2050</v>
       </c>
@@ -40019,7 +40009,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:23">
       <c r="B366">
         <v>2050</v>
       </c>
@@ -40088,7 +40078,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:23">
       <c r="B367">
         <v>2050</v>
       </c>
@@ -40157,7 +40147,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:23">
       <c r="B368">
         <v>2050</v>
       </c>
@@ -40226,7 +40216,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:23">
       <c r="B369">
         <v>2050</v>
       </c>
@@ -40295,7 +40285,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:23">
       <c r="B370">
         <v>2050</v>
       </c>
@@ -40364,7 +40354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="371" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:23">
       <c r="B371">
         <v>2050</v>
       </c>
@@ -40433,7 +40423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="372" spans="2:23" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:23">
       <c r="B372">
         <v>2050</v>
       </c>
@@ -40510,7 +40500,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87145D13-828E-41C5-975E-33BB80D91FFB}">
   <dimension ref="A1:BC137"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="25" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.140625" customWidth="1"/>
@@ -40518,7 +40508,7 @@
     <col min="4" max="33" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36">
       <c r="A1" s="20" t="s">
         <v>140</v>
       </c>
@@ -40616,7 +40606,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:36">
       <c r="A2" s="73" t="s">
         <v>141</v>
       </c>
@@ -40716,7 +40706,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:36">
       <c r="A3" s="73" t="s">
         <v>142</v>
       </c>
@@ -40816,7 +40806,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36">
       <c r="A4" s="73" t="s">
         <v>143</v>
       </c>
@@ -40916,7 +40906,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36">
       <c r="A5" s="73" t="s">
         <v>144</v>
       </c>
@@ -41016,7 +41006,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36">
       <c r="A6" s="73" t="s">
         <v>145</v>
       </c>
@@ -41116,7 +41106,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36">
       <c r="A7" s="73" t="s">
         <v>146</v>
       </c>
@@ -41216,7 +41206,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36">
       <c r="A8" s="73" t="s">
         <v>147</v>
       </c>
@@ -41316,7 +41306,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36">
       <c r="A9" s="73" t="s">
         <v>148</v>
       </c>
@@ -41416,7 +41406,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36">
       <c r="A10" s="73" t="s">
         <v>149</v>
       </c>
@@ -41516,7 +41506,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36">
       <c r="A11" s="73" t="s">
         <v>150</v>
       </c>
@@ -41616,12 +41606,12 @@
         <v>646</v>
       </c>
     </row>
-    <row r="14" spans="1:36" s="76" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" s="76" customFormat="1" ht="12.75">
       <c r="A14" s="75" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="15" spans="1:36" s="75" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" s="75" customFormat="1" ht="12.75">
       <c r="A15" s="77"/>
       <c r="B15" s="75">
         <v>2020</v>
@@ -41729,7 +41719,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="16" spans="1:36" s="77" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" s="77" customFormat="1" ht="12.75">
       <c r="A16" s="78" t="s">
         <v>153</v>
       </c>
@@ -41755,7 +41745,7 @@
       <c r="U16" s="79"/>
       <c r="V16" s="79"/>
     </row>
-    <row r="17" spans="1:36" s="76" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:36" s="76" customFormat="1" ht="12.75">
       <c r="A17" s="76" t="s">
         <v>141</v>
       </c>
@@ -41894,7 +41884,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="18" spans="1:36" s="76" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:36" s="76" customFormat="1" ht="12.75">
       <c r="A18" s="76" t="s">
         <v>142</v>
       </c>
@@ -42033,7 +42023,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="19" spans="1:36" s="76" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:36" s="76" customFormat="1" ht="12.75">
       <c r="A19" s="76" t="s">
         <v>143</v>
       </c>
@@ -42172,7 +42162,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="20" spans="1:36" s="76" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:36" s="76" customFormat="1" ht="12.75">
       <c r="A20" s="76" t="s">
         <v>144</v>
       </c>
@@ -42311,7 +42301,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="21" spans="1:36" s="76" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:36" s="76" customFormat="1" ht="12.75">
       <c r="A21" s="76" t="s">
         <v>145</v>
       </c>
@@ -42450,7 +42440,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="22" spans="1:36" s="76" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:36" s="76" customFormat="1" ht="12.75">
       <c r="A22" s="76" t="s">
         <v>146</v>
       </c>
@@ -42589,7 +42579,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="23" spans="1:36" s="84" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:36" s="84" customFormat="1" ht="12.75">
       <c r="A23" s="82" t="s">
         <v>156</v>
       </c>
@@ -42643,7 +42633,7 @@
       <c r="AH23" s="81"/>
       <c r="AI23" s="81"/>
     </row>
-    <row r="24" spans="1:36" s="76" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:36" s="76" customFormat="1" ht="12.75">
       <c r="A24" s="76" t="s">
         <v>147</v>
       </c>
@@ -42782,7 +42772,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="25" spans="1:36" s="76" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:36" s="76" customFormat="1" ht="12.75">
       <c r="A25" s="76" t="s">
         <v>148</v>
       </c>
@@ -42921,7 +42911,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="26" spans="1:36" s="76" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:36" s="76" customFormat="1" ht="12.75">
       <c r="A26" s="76" t="s">
         <v>149</v>
       </c>
@@ -43060,7 +43050,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="27" spans="1:36" s="76" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:36" s="76" customFormat="1" ht="12.75">
       <c r="A27" s="76" t="s">
         <v>150</v>
       </c>
@@ -43199,7 +43189,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="28" spans="1:36" s="84" customFormat="1" ht="12.75" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:36" s="84" customFormat="1" ht="12.75">
       <c r="A28" s="82" t="s">
         <v>158</v>
       </c>
@@ -43253,17 +43243,17 @@
       <c r="AH28" s="80"/>
       <c r="AI28" s="80"/>
     </row>
-    <row r="31" spans="1:36" s="85" customFormat="1" ht="33.75" x14ac:dyDescent="0.5">
+    <row r="31" spans="1:36" s="85" customFormat="1" ht="33.75">
       <c r="B31" s="86" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="32" spans="1:36" s="85" customFormat="1" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:36" s="85" customFormat="1" ht="17.25" customHeight="1">
       <c r="B32" s="85" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="33" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="B33" s="85" t="s">
         <v>161</v>
       </c>
@@ -43427,7 +43417,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="34" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A34" s="85" t="s">
         <v>164</v>
       </c>
@@ -43591,7 +43581,7 @@
         <v>8941.1253098647539</v>
       </c>
     </row>
-    <row r="35" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A35" s="85" t="s">
         <v>164</v>
       </c>
@@ -43755,7 +43745,7 @@
         <v>9335.2229055276457</v>
       </c>
     </row>
-    <row r="36" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A36" s="85" t="s">
         <v>164</v>
       </c>
@@ -43919,7 +43909,7 @@
         <v>9449.9949414654075</v>
       </c>
     </row>
-    <row r="37" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A37" s="85" t="s">
         <v>164</v>
       </c>
@@ -44083,7 +44073,7 @@
         <v>49876.035846764251</v>
       </c>
     </row>
-    <row r="38" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A38" s="12" t="s">
         <v>150</v>
       </c>
@@ -44247,7 +44237,7 @@
         <v>48998.777404870685</v>
       </c>
     </row>
-    <row r="39" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A39" s="12" t="s">
         <v>150</v>
       </c>
@@ -44411,7 +44401,7 @@
         <v>48193.856381193618</v>
       </c>
     </row>
-    <row r="40" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A40" s="12" t="s">
         <v>147</v>
       </c>
@@ -44575,7 +44565,7 @@
         <v>16842.299684166632</v>
       </c>
     </row>
-    <row r="41" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A41" s="12" t="s">
         <v>149</v>
       </c>
@@ -44739,7 +44729,7 @@
         <v>16665.30579126858</v>
       </c>
     </row>
-    <row r="42" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A42" s="12" t="s">
         <v>149</v>
       </c>
@@ -44903,7 +44893,7 @@
         <v>16757.077087471102</v>
       </c>
     </row>
-    <row r="43" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A43" s="12" t="s">
         <v>147</v>
       </c>
@@ -45067,7 +45057,7 @@
         <v>49997.893522427854</v>
       </c>
     </row>
-    <row r="44" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A44" s="12" t="s">
         <v>148</v>
       </c>
@@ -45231,7 +45221,7 @@
         <v>49806.329843386644</v>
       </c>
     </row>
-    <row r="45" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A45" s="12" t="s">
         <v>148</v>
       </c>
@@ -45395,7 +45385,7 @@
         <v>32848.683068259023</v>
       </c>
     </row>
-    <row r="46" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A46" s="85" t="s">
         <v>164</v>
       </c>
@@ -45559,7 +45549,7 @@
         <v>49918.549378741227</v>
       </c>
     </row>
-    <row r="47" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A47" s="85" t="s">
         <v>178</v>
       </c>
@@ -45723,7 +45713,7 @@
         <v>19869.544927123421</v>
       </c>
     </row>
-    <row r="48" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A48" s="85" t="s">
         <v>178</v>
       </c>
@@ -45887,7 +45877,7 @@
         <v>20407.15243008138</v>
       </c>
     </row>
-    <row r="49" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A49" s="85" t="s">
         <v>178</v>
       </c>
@@ -46051,7 +46041,7 @@
         <v>20211.770846553783</v>
       </c>
     </row>
-    <row r="50" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A50" s="85" t="s">
         <v>178</v>
       </c>
@@ -46215,7 +46205,7 @@
         <v>3807.8853271450416</v>
       </c>
     </row>
-    <row r="51" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A51" s="85" t="s">
         <v>178</v>
       </c>
@@ -46379,7 +46369,7 @@
         <v>18552.652863838659</v>
       </c>
     </row>
-    <row r="52" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A52" s="85" t="s">
         <v>178</v>
       </c>
@@ -46543,7 +46533,7 @@
         <v>19882.163050778829</v>
       </c>
     </row>
-    <row r="53" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A53" s="85" t="s">
         <v>178</v>
       </c>
@@ -46707,7 +46697,7 @@
         <v>7249.3066990766138</v>
       </c>
     </row>
-    <row r="54" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A54" s="85" t="s">
         <v>178</v>
       </c>
@@ -46871,7 +46861,7 @@
         <v>9896.7090327829428</v>
       </c>
     </row>
-    <row r="55" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A55" s="85" t="s">
         <v>178</v>
       </c>
@@ -47035,7 +47025,7 @@
         <v>35740.823754379227</v>
       </c>
     </row>
-    <row r="56" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A56" s="85" t="s">
         <v>178</v>
       </c>
@@ -47199,7 +47189,7 @@
         <v>23790.748009964722</v>
       </c>
     </row>
-    <row r="57" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A57" s="12" t="s">
         <v>145</v>
       </c>
@@ -47363,7 +47353,7 @@
         <v>166426.06571909611</v>
       </c>
     </row>
-    <row r="58" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A58" s="12" t="s">
         <v>145</v>
       </c>
@@ -47527,7 +47517,7 @@
         <v>38356.83368908472</v>
       </c>
     </row>
-    <row r="59" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A59" s="12" t="s">
         <v>145</v>
       </c>
@@ -47691,7 +47681,7 @@
         <v>155258.70386157703</v>
       </c>
     </row>
-    <row r="60" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A60" s="12" t="s">
         <v>144</v>
       </c>
@@ -47855,7 +47845,7 @@
         <v>78994.790843715484</v>
       </c>
     </row>
-    <row r="61" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A61" s="12" t="s">
         <v>144</v>
       </c>
@@ -48019,7 +48009,7 @@
         <v>68790.444903315016</v>
       </c>
     </row>
-    <row r="62" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A62" s="12" t="s">
         <v>144</v>
       </c>
@@ -48183,7 +48173,7 @@
         <v>68126.066685689249</v>
       </c>
     </row>
-    <row r="63" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A63" s="12" t="s">
         <v>146</v>
       </c>
@@ -48347,7 +48337,7 @@
         <v>11871.71555095992</v>
       </c>
     </row>
-    <row r="64" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A64" s="12" t="s">
         <v>146</v>
       </c>
@@ -48511,7 +48501,7 @@
         <v>34354.151463321126</v>
       </c>
     </row>
-    <row r="65" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A65" s="12" t="s">
         <v>146</v>
       </c>
@@ -48675,7 +48665,7 @@
         <v>34961.745255937552</v>
       </c>
     </row>
-    <row r="66" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A66" s="12" t="s">
         <v>141</v>
       </c>
@@ -48839,7 +48829,7 @@
         <v>38399.901376300746</v>
       </c>
     </row>
-    <row r="67" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A67" s="12" t="s">
         <v>142</v>
       </c>
@@ -49003,7 +48993,7 @@
         <v>33700.276020704143</v>
       </c>
     </row>
-    <row r="68" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A68" s="12" t="s">
         <v>143</v>
       </c>
@@ -49167,7 +49157,7 @@
         <v>35644.527293675485</v>
       </c>
     </row>
-    <row r="69" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A69" s="12" t="s">
         <v>141</v>
       </c>
@@ -49331,7 +49321,7 @@
         <v>24778.887723792297</v>
       </c>
     </row>
-    <row r="70" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A70" s="12" t="s">
         <v>142</v>
       </c>
@@ -49495,7 +49485,7 @@
         <v>22251.772967826735</v>
       </c>
     </row>
-    <row r="71" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A71" s="12" t="s">
         <v>143</v>
       </c>
@@ -49659,12 +49649,12 @@
         <v>23473.477713170843</v>
       </c>
     </row>
-    <row r="72" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="B72" s="85" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="73" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="B73" s="85" t="s">
         <v>163</v>
       </c>
@@ -49825,9 +49815,9 @@
         <v>36810.263386482577</v>
       </c>
     </row>
-    <row r="74" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="75" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="76" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:55" s="85" customFormat="1" ht="15.75"/>
+    <row r="75" spans="1:55" s="85" customFormat="1" ht="15.75"/>
+    <row r="76" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A76" s="20" t="s">
         <v>204</v>
       </c>
@@ -49931,7 +49921,7 @@
       <c r="AI76" s="87"/>
       <c r="AJ76" s="87"/>
     </row>
-    <row r="77" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A77" s="12" t="s">
         <v>141</v>
       </c>
@@ -50067,7 +50057,7 @@
       <c r="AI77" s="88"/>
       <c r="AJ77" s="88"/>
     </row>
-    <row r="78" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A78" s="12" t="s">
         <v>142</v>
       </c>
@@ -50203,7 +50193,7 @@
       <c r="AI78" s="88"/>
       <c r="AJ78" s="88"/>
     </row>
-    <row r="79" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A79" s="12" t="s">
         <v>143</v>
       </c>
@@ -50339,7 +50329,7 @@
       <c r="AI79" s="88"/>
       <c r="AJ79" s="88"/>
     </row>
-    <row r="80" spans="1:55" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:55" s="85" customFormat="1" ht="15.75">
       <c r="A80" s="12" t="s">
         <v>144</v>
       </c>
@@ -50475,7 +50465,7 @@
       <c r="AI80" s="88"/>
       <c r="AJ80" s="88"/>
     </row>
-    <row r="81" spans="1:36" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:36" s="85" customFormat="1" ht="15.75">
       <c r="A81" s="12" t="s">
         <v>145</v>
       </c>
@@ -50611,7 +50601,7 @@
       <c r="AI81" s="88"/>
       <c r="AJ81" s="88"/>
     </row>
-    <row r="82" spans="1:36" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:36" s="85" customFormat="1" ht="15.75">
       <c r="A82" s="12" t="s">
         <v>146</v>
       </c>
@@ -50747,7 +50737,7 @@
       <c r="AI82" s="88"/>
       <c r="AJ82" s="88"/>
     </row>
-    <row r="83" spans="1:36" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:36" s="85" customFormat="1" ht="15.75">
       <c r="A83" s="12" t="s">
         <v>147</v>
       </c>
@@ -50883,7 +50873,7 @@
       <c r="AI83" s="88"/>
       <c r="AJ83" s="88"/>
     </row>
-    <row r="84" spans="1:36" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:36" s="85" customFormat="1" ht="15.75">
       <c r="A84" s="12" t="s">
         <v>148</v>
       </c>
@@ -51019,7 +51009,7 @@
       <c r="AI84" s="88"/>
       <c r="AJ84" s="88"/>
     </row>
-    <row r="85" spans="1:36" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:36" s="85" customFormat="1" ht="15.75">
       <c r="A85" s="12" t="s">
         <v>149</v>
       </c>
@@ -51155,7 +51145,7 @@
       <c r="AI85" s="88"/>
       <c r="AJ85" s="88"/>
     </row>
-    <row r="86" spans="1:36" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:36" s="85" customFormat="1" ht="15.75">
       <c r="A86" s="12" t="s">
         <v>150</v>
       </c>
@@ -51291,8 +51281,8 @@
       <c r="AI86" s="88"/>
       <c r="AJ86" s="88"/>
     </row>
-    <row r="87" spans="1:36" s="85" customFormat="1" ht="15.75" x14ac:dyDescent="0.25"/>
-    <row r="88" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:36" s="85" customFormat="1" ht="15.75"/>
+    <row r="88" spans="1:36" ht="15.75">
       <c r="A88" s="20" t="s">
         <v>206</v>
       </c>
@@ -51393,7 +51383,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="89" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:36" ht="15.75">
       <c r="A89" s="12" t="s">
         <v>141</v>
       </c>
@@ -51526,7 +51516,7 @@
         <v>5996857491.3620796</v>
       </c>
     </row>
-    <row r="90" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:36" ht="15.75">
       <c r="A90" s="12" t="s">
         <v>142</v>
       </c>
@@ -51659,7 +51649,7 @@
         <v>6092649373.6413736</v>
       </c>
     </row>
-    <row r="91" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:36" ht="15.75">
       <c r="A91" s="12" t="s">
         <v>143</v>
       </c>
@@ -51792,7 +51782,7 @@
         <v>4921899033.8039122</v>
       </c>
     </row>
-    <row r="92" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:36" ht="15.75">
       <c r="A92" s="12" t="s">
         <v>144</v>
       </c>
@@ -51925,7 +51915,7 @@
         <v>4009203689.6150379</v>
       </c>
     </row>
-    <row r="93" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:36" ht="15.75">
       <c r="A93" s="12" t="s">
         <v>145</v>
       </c>
@@ -52058,7 +52048,7 @@
         <v>13858416762.7997</v>
       </c>
     </row>
-    <row r="94" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:36" ht="15.75">
       <c r="A94" s="12" t="s">
         <v>146</v>
       </c>
@@ -52191,7 +52181,7 @@
         <v>202489837.31678164</v>
       </c>
     </row>
-    <row r="95" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:36" ht="15.75">
       <c r="A95" s="12" t="s">
         <v>147</v>
       </c>
@@ -52324,7 +52314,7 @@
         <v>270851560.49265301</v>
       </c>
     </row>
-    <row r="96" spans="1:36" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:36" ht="15.75">
       <c r="A96" s="12" t="s">
         <v>148</v>
       </c>
@@ -52457,7 +52447,7 @@
         <v>305107518.63828403</v>
       </c>
     </row>
-    <row r="97" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:33" ht="15.75">
       <c r="A97" s="12" t="s">
         <v>149</v>
       </c>
@@ -52590,7 +52580,7 @@
         <v>648709168.4910059</v>
       </c>
     </row>
-    <row r="98" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:33" ht="15.75">
       <c r="A98" s="12" t="s">
         <v>150</v>
       </c>
@@ -52723,7 +52713,7 @@
         <v>1128440351.9515312</v>
       </c>
     </row>
-    <row r="100" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:33" ht="15.75">
       <c r="A100" s="20" t="s">
         <v>207</v>
       </c>
@@ -52824,7 +52814,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="101" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:33" ht="15.75">
       <c r="A101" s="12" t="s">
         <v>141</v>
       </c>
@@ -52957,7 +52947,7 @@
         <v>0.49603822209834753</v>
       </c>
     </row>
-    <row r="102" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:33" ht="15.75">
       <c r="A102" s="12" t="s">
         <v>142</v>
       </c>
@@ -53090,7 +53080,7 @@
         <v>0.50396177790165253</v>
       </c>
     </row>
-    <row r="103" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:33" ht="15.75">
       <c r="A103" s="12" t="s">
         <v>143</v>
       </c>
@@ -53223,7 +53213,7 @@
         <v>0.21406998251195397</v>
       </c>
     </row>
-    <row r="104" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:33" ht="15.75">
       <c r="A104" s="12" t="s">
         <v>144</v>
       </c>
@@ -53356,7 +53346,7 @@
         <v>0.17437378496150294</v>
       </c>
     </row>
-    <row r="105" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:33" ht="15.75">
       <c r="A105" s="12" t="s">
         <v>145</v>
       </c>
@@ -53489,7 +53479,7 @@
         <v>0.60274926683392283</v>
       </c>
     </row>
-    <row r="106" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:33" ht="15.75">
       <c r="A106" s="12" t="s">
         <v>146</v>
       </c>
@@ -53622,7 +53612,7 @@
         <v>8.806965692620258E-3</v>
       </c>
     </row>
-    <row r="107" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:33" ht="15.75">
       <c r="A107" s="12" t="s">
         <v>147</v>
       </c>
@@ -53755,7 +53745,7 @@
         <v>0.11510372302483096</v>
       </c>
     </row>
-    <row r="108" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:33" ht="15.75">
       <c r="A108" s="12" t="s">
         <v>148</v>
       </c>
@@ -53888,7 +53878,7 @@
         <v>0.12966146938292097</v>
       </c>
     </row>
-    <row r="109" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:33" ht="15.75">
       <c r="A109" s="12" t="s">
         <v>149</v>
       </c>
@@ -54021,7 +54011,7 @@
         <v>0.27568178052155834</v>
       </c>
     </row>
-    <row r="110" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:33" ht="15.75">
       <c r="A110" s="12" t="s">
         <v>150</v>
       </c>
@@ -54154,7 +54144,7 @@
         <v>0.47955302707068981</v>
       </c>
     </row>
-    <row r="111" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:33" ht="15.75">
       <c r="A111" s="12"/>
       <c r="B111" s="87"/>
       <c r="C111" s="89"/>
@@ -54189,7 +54179,7 @@
       <c r="AF111" s="89"/>
       <c r="AG111" s="89"/>
     </row>
-    <row r="112" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:33" ht="15.75">
       <c r="A112" s="12" t="s">
         <v>251</v>
       </c>
@@ -54319,7 +54309,7 @@
         <v>0.58604270197066977</v>
       </c>
     </row>
-    <row r="113" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:33" ht="15.75">
       <c r="A113" s="12" t="s">
         <v>252</v>
       </c>
@@ -54449,7 +54439,7 @@
         <v>0.41395729802933023</v>
       </c>
     </row>
-    <row r="114" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:33" ht="15.75">
       <c r="A114" s="12"/>
       <c r="B114" s="87"/>
       <c r="C114" s="89"/>
@@ -54484,7 +54474,7 @@
       <c r="AF114" s="89"/>
       <c r="AG114" s="89"/>
     </row>
-    <row r="115" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:33" ht="15.75">
       <c r="A115" s="12"/>
       <c r="B115" s="87"/>
       <c r="C115" s="89"/>
@@ -54519,7 +54509,7 @@
       <c r="AF115" s="89"/>
       <c r="AG115" s="89"/>
     </row>
-    <row r="116" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:33" ht="15.75">
       <c r="A116" s="20" t="s">
         <v>208</v>
       </c>
@@ -54620,7 +54610,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="117" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:33" ht="15.75">
       <c r="A117" s="12" t="s">
         <v>141</v>
       </c>
@@ -54753,7 +54743,7 @@
         <v>56.052319097113269</v>
       </c>
     </row>
-    <row r="118" spans="1:33" s="103" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:33" s="103" customFormat="1" ht="15.75">
       <c r="A118" s="101" t="s">
         <v>253</v>
       </c>
@@ -54885,7 +54875,7 @@
         <v>50.50367386395402</v>
       </c>
     </row>
-    <row r="119" spans="1:33" s="103" customFormat="1" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:33" s="103" customFormat="1" ht="15.75">
       <c r="A119" s="101" t="s">
         <v>254</v>
       </c>
@@ -55017,7 +55007,7 @@
         <v>35.673790157228566</v>
       </c>
     </row>
-    <row r="120" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:33" ht="15.75">
       <c r="A120" s="12" t="s">
         <v>143</v>
       </c>
@@ -55150,7 +55140,7 @@
         <v>64.220994753586197</v>
       </c>
     </row>
-    <row r="121" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:33" ht="15.75">
       <c r="A121" s="12" t="s">
         <v>144</v>
       </c>
@@ -55283,7 +55273,7 @@
         <v>58.066470392180477</v>
       </c>
     </row>
-    <row r="122" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:33" ht="15.75">
       <c r="A122" s="12" t="s">
         <v>145</v>
       </c>
@@ -55416,7 +55406,7 @@
         <v>399.62276391089085</v>
       </c>
     </row>
-    <row r="123" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:33" ht="15.75">
       <c r="A123" s="12" t="s">
         <v>146</v>
       </c>
@@ -55549,7 +55539,7 @@
         <v>2.7477732960975203</v>
       </c>
     </row>
-    <row r="124" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:33" ht="15.75">
       <c r="A124" s="12" t="s">
         <v>147</v>
       </c>
@@ -55682,7 +55672,7 @@
         <v>13.236928147855561</v>
       </c>
     </row>
-    <row r="125" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:33" ht="15.75">
       <c r="A125" s="12" t="s">
         <v>148</v>
       </c>
@@ -55815,7 +55805,7 @@
         <v>55.754431834656017</v>
       </c>
     </row>
-    <row r="126" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:33" ht="15.75">
       <c r="A126" s="12" t="s">
         <v>149</v>
       </c>
@@ -55948,7 +55938,7 @@
         <v>47.417266249708035</v>
       </c>
     </row>
-    <row r="127" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:33" ht="15.75">
       <c r="A127" s="12" t="s">
         <v>150</v>
       </c>
@@ -56081,10 +56071,10 @@
         <v>309.79125548766564</v>
       </c>
     </row>
-    <row r="128" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:33">
       <c r="A128" s="20"/>
     </row>
-    <row r="129" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:33" ht="15.75">
       <c r="A129" s="20" t="s">
         <v>209</v>
       </c>
@@ -56182,7 +56172,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="130" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:33">
       <c r="A130" s="12" t="s">
         <v>154</v>
       </c>
@@ -56311,7 +56301,7 @@
         <v>106.55599296106729</v>
       </c>
     </row>
-    <row r="131" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:33">
       <c r="A131" s="12" t="s">
         <v>155</v>
       </c>
@@ -56440,7 +56430,7 @@
         <v>560.33179250998364</v>
       </c>
     </row>
-    <row r="132" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:33">
       <c r="A132" s="12" t="s">
         <v>157</v>
       </c>
@@ -56569,7 +56559,7 @@
         <v>426.19988171988524</v>
       </c>
     </row>
-    <row r="134" spans="1:33" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:33" ht="15.75">
       <c r="A134" s="20" t="s">
         <v>210</v>
       </c>
@@ -56667,7 +56657,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="135" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:33">
       <c r="A135" s="12" t="s">
         <v>154</v>
       </c>
@@ -56795,7 +56785,7 @@
         <v>-2.7263052731958393E-3</v>
       </c>
     </row>
-    <row r="136" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:33">
       <c r="A136" s="12" t="s">
         <v>155</v>
       </c>
@@ -56923,7 +56913,7 @@
         <v>1.2829792993040989E-3</v>
       </c>
     </row>
-    <row r="137" spans="1:33" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:33">
       <c r="A137" s="12" t="s">
         <v>157</v>
       </c>
@@ -57062,7 +57052,7 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.5703125" customWidth="1"/>
     <col min="2" max="5" width="18.5703125" customWidth="1"/>
@@ -57072,7 +57062,7 @@
     <col min="9" max="9" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="30">
       <c r="A1" s="9" t="s">
         <v>40</v>
       </c>
@@ -57101,7 +57091,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -57132,7 +57122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
@@ -57162,7 +57152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -57191,7 +57181,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -57220,7 +57210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
@@ -57249,7 +57239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
@@ -57290,7 +57280,7 @@
     <tabColor theme="8" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:I7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
     <col min="2" max="5" width="18.5703125" customWidth="1"/>
@@ -57300,7 +57290,7 @@
     <col min="9" max="9" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="60">
       <c r="A1" s="9" t="s">
         <v>40</v>
       </c>
@@ -57329,7 +57319,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
         <v>26</v>
       </c>
@@ -57360,7 +57350,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
         <v>27</v>
       </c>
@@ -57390,7 +57380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
         <v>28</v>
       </c>
@@ -57419,7 +57409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
         <v>29</v>
       </c>
@@ -57448,7 +57438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
         <v>30</v>
       </c>
@@ -57477,7 +57467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
         <v>31</v>
       </c>
